--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\OneDrive\Desktop\AIIMS REWARI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4818BF0C-29A6-495B-AFB5-98BEC1DB1199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFBC2F0-927A-4861-8DDA-E46D52E12B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{0D064328-DC67-411D-BEE3-DF99AB8C76F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="OPD" sheetId="1" r:id="rId1"/>
-    <sheet name="EMR" sheetId="2" r:id="rId2"/>
+    <sheet name="OPD Backup" sheetId="1" r:id="rId1"/>
+    <sheet name="EMR Backup" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -750,38 +750,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
@@ -861,9 +831,6 @@
     <xf numFmtId="166" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="7">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -924,6 +891,39 @@
     <xf numFmtId="9" fontId="21" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Activity" xfId="7" xr:uid="{E08172A1-BC2B-4459-AE80-8AFA72797A70}"/>
@@ -957,243 +957,6 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="EMR"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="OPD"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>OPD Balance Activities Schedule (11-Sep-2026)</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="str">
-            <v>Electrical</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55" t="str">
-            <v>Wiring</v>
-          </cell>
-          <cell r="C55" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D55">
-            <v>46325</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="B56" t="str">
-            <v>Cable Laying &amp; Panel Installation</v>
-          </cell>
-          <cell r="C56" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D56">
-            <v>46325</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="B57" t="str">
-            <v>UPS Installation</v>
-          </cell>
-          <cell r="C57">
-            <v>46291</v>
-          </cell>
-          <cell r="D57">
-            <v>46305</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="B58" t="str">
-            <v>DB Dresssing</v>
-          </cell>
-          <cell r="C58" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D58">
-            <v>46336</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="B59" t="str">
-            <v>PHE</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="B60" t="str">
-            <v>Cister&amp; Sensor Fixing</v>
-          </cell>
-          <cell r="C60" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D60">
-            <v>46288</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>HVAC</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62" t="str">
-            <v>Duct testinfg &amp; dropper for diffusere</v>
-          </cell>
-          <cell r="C62" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D62">
-            <v>46366</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="B63" t="str">
-            <v>Pipe Testing</v>
-          </cell>
-          <cell r="C63" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D63">
-            <v>46310</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="B64" t="str">
-            <v>AHU Connection</v>
-          </cell>
-          <cell r="C64" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D64">
-            <v>46311</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="B65" t="str">
-            <v>Firefighting</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="B66" t="str">
-            <v>Sprinkler Flexible connection &amp; testing</v>
-          </cell>
-          <cell r="C66" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D66">
-            <v>46340</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="B67" t="str">
-            <v>Wet Riser &amp; FHC installation</v>
-          </cell>
-          <cell r="C67" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D67">
-            <v>46319</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="B68" t="str">
-            <v>ELV</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="B69" t="str">
-            <v>CAT 6 cabling</v>
-          </cell>
-          <cell r="C69" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D69">
-            <v>46341</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70" t="str">
-            <v>PA &amp; FAS cabling</v>
-          </cell>
-          <cell r="C70" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D70">
-            <v>46341</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71" t="str">
-            <v>Fire Panel Installation</v>
-          </cell>
-          <cell r="C71">
-            <v>46291</v>
-          </cell>
-          <cell r="D71">
-            <v>46295</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72" t="str">
-            <v>Network Switch Installation &amp; connection</v>
-          </cell>
-          <cell r="C72" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D72">
-            <v>46346</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73" t="str">
-            <v>MGPS</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74" t="str">
-            <v>Copper Pipe testing</v>
-          </cell>
-          <cell r="C74">
-            <v>46310</v>
-          </cell>
-          <cell r="D74">
-            <v>46371</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75" t="str">
-            <v>PTTS</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76" t="str">
-            <v>Pipe accessories fixing &amp; testing</v>
-          </cell>
-          <cell r="C76" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D76">
-            <v>46386</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="EMR"/>
       <sheetName val="OPD"/>
       <sheetName val="IPD"/>
     </sheetNames>
@@ -2321,7 +2084,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3409,6 +3172,243 @@
       <sheetData sheetId="12" refreshError="1"/>
       <sheetData sheetId="13" refreshError="1"/>
       <sheetData sheetId="14" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="EMR"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="OPD"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>OPD Balance Activities Schedule (11-Sep-2026)</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54" t="str">
+            <v>Electrical</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55" t="str">
+            <v>Wiring</v>
+          </cell>
+          <cell r="C55" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D55">
+            <v>46325</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56" t="str">
+            <v>Cable Laying &amp; Panel Installation</v>
+          </cell>
+          <cell r="C56" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D56">
+            <v>46325</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57" t="str">
+            <v>UPS Installation</v>
+          </cell>
+          <cell r="C57">
+            <v>46291</v>
+          </cell>
+          <cell r="D57">
+            <v>46305</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58" t="str">
+            <v>DB Dresssing</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D58">
+            <v>46336</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59" t="str">
+            <v>PHE</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>Cister&amp; Sensor Fixing</v>
+          </cell>
+          <cell r="C60" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D60">
+            <v>46288</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>HVAC</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62" t="str">
+            <v>Duct testinfg &amp; dropper for diffusere</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D62">
+            <v>46366</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="B63" t="str">
+            <v>Pipe Testing</v>
+          </cell>
+          <cell r="C63" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D63">
+            <v>46310</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="B64" t="str">
+            <v>AHU Connection</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D64">
+            <v>46311</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="B65" t="str">
+            <v>Firefighting</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="B66" t="str">
+            <v>Sprinkler Flexible connection &amp; testing</v>
+          </cell>
+          <cell r="C66" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D66">
+            <v>46340</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="B67" t="str">
+            <v>Wet Riser &amp; FHC installation</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D67">
+            <v>46319</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="B68" t="str">
+            <v>ELV</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="B69" t="str">
+            <v>CAT 6 cabling</v>
+          </cell>
+          <cell r="C69" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D69">
+            <v>46341</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70" t="str">
+            <v>PA &amp; FAS cabling</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D70">
+            <v>46341</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71" t="str">
+            <v>Fire Panel Installation</v>
+          </cell>
+          <cell r="C71">
+            <v>46291</v>
+          </cell>
+          <cell r="D71">
+            <v>46295</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="B72" t="str">
+            <v>Network Switch Installation &amp; connection</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D72">
+            <v>46346</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="B73" t="str">
+            <v>MGPS</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="B74" t="str">
+            <v>Copper Pipe testing</v>
+          </cell>
+          <cell r="C74">
+            <v>46310</v>
+          </cell>
+          <cell r="D74">
+            <v>46371</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="B75" t="str">
+            <v>PTTS</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="B76" t="str">
+            <v>Pipe accessories fixing &amp; testing</v>
+          </cell>
+          <cell r="C76" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D76">
+            <v>46386</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3734,13 +3734,13 @@
   <dimension ref="A1:L1048571"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="43.08984375" style="46" customWidth="1"/>
-    <col min="2" max="3" width="14.54296875" style="47" customWidth="1"/>
+    <col min="1" max="1" width="43.08984375" style="35" customWidth="1"/>
+    <col min="2" max="3" width="14.54296875" style="36" customWidth="1"/>
     <col min="4" max="4" width="14.54296875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" style="48" customWidth="1"/>
-    <col min="6" max="7" width="14.54296875" style="49" customWidth="1"/>
-    <col min="8" max="11" width="14.54296875" style="48" customWidth="1"/>
-    <col min="12" max="12" width="32.54296875" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" style="37" customWidth="1"/>
+    <col min="6" max="7" width="14.54296875" style="38" customWidth="1"/>
+    <col min="8" max="11" width="14.54296875" style="37" customWidth="1"/>
+    <col min="12" max="12" width="32.54296875" style="37" bestFit="1" customWidth="1"/>
     <col min="13" max="21" width="3" style="7"/>
     <col min="22" max="22" width="5.1796875" style="7" bestFit="1" customWidth="1"/>
     <col min="23" max="16384" width="3" style="7"/>
@@ -3762,2898 +3762,2898 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:12" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:12" s="8" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="56" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="15">
         <v>45910</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="15">
         <v>46305</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="17">
         <v>4151</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="17">
         <v>4115.45</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="18">
         <f>F5/E5</f>
         <v>0.99143579860274633</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="17">
         <f>(E5-F5)*G5</f>
         <v>35.245542640327812</v>
       </c>
-      <c r="I5" s="27" t="e">
+      <c r="I5" s="17" t="e">
         <f ca="1">H5/(C5-(IF(B5&gt;TODAY(),B5,TODAY())))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J5" s="27" t="e">
+      <c r="J5" s="17" t="e">
         <f ca="1">ROUND(I5/1,0)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="17">
         <v>65</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="17"/>
     </row>
     <row r="6" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="15">
         <v>45991</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="15">
         <v>46320</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="17">
         <v>50950</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="17">
         <v>50087.5</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="18">
         <f>F6/E6</f>
         <v>0.98307163886162907</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="17">
         <f>(E6-F6)*G6</f>
         <v>847.89928851815512</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="17">
         <f ca="1">H6/(C6-(IF(B6&gt;TODAY(),B6,TODAY())))</f>
         <v>56.526619234543674</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="17">
         <f ca="1">ROUND(I6/10,0)</f>
         <v>6</v>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="17">
         <v>7</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="17"/>
     </row>
     <row r="7" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="15">
         <v>46047</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="15">
         <v>46341</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="17">
         <f>206+511</f>
         <v>717</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="17">
         <v>378</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="18">
         <f>F7/E7</f>
         <v>0.52719665271966532</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="17">
         <f>(E7-F7)*G7</f>
         <v>178.71966527196653</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="17">
         <f ca="1">H7/(C7-(IF(B7&gt;TODAY(),B7,TODAY())))</f>
         <v>4.964435146443515</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="17">
         <f ca="1">ROUND(I7/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="17">
         <v>14</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="15">
         <v>46009</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="15">
         <v>46351</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="17">
         <v>29200</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="17">
         <v>22255</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="20">
         <f t="shared" ref="G8:G15" si="0">F8/E8</f>
         <v>0.7621575342465754</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="17">
         <f t="shared" ref="H8:H15" si="1">(E8-F8)*G8</f>
         <v>5293.1840753424658</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="17">
         <f t="shared" ref="I8:I15" ca="1" si="2">H8/(C8-(IF(B8&gt;TODAY(),B8,TODAY())))</f>
         <v>115.06921902918404</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="17">
         <f t="shared" ref="J8" ca="1" si="3">ROUND(I8/3,0)</f>
         <v>38</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="17">
         <v>30</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="15">
         <v>46211</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="15">
         <v>46310</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="17">
         <v>4152</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="17">
         <v>2283.6000000000004</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="20">
         <f t="shared" si="0"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="17">
         <f t="shared" si="1"/>
         <v>1027.6199999999999</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>205.52399999999997</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="17">
         <f ca="1">ROUND(I9/12,0)</f>
         <v>17</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="17">
         <v>9</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="15">
         <v>46270</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="15">
         <v>46323</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="17">
         <v>3598</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="17">
         <v>408</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="20">
         <f t="shared" si="0"/>
         <v>0.11339633129516398</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="17">
         <f t="shared" si="1"/>
         <v>361.73429683157309</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>20.096349823976283</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="17">
         <f ca="1">ROUND(I10/12,0)</f>
         <v>2</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="17">
         <v>5</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="15">
         <v>46331</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="15">
         <v>46346</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="17">
         <v>3598</v>
       </c>
-      <c r="F11" s="27">
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
+      <c r="F11" s="17">
+        <v>0</v>
+      </c>
+      <c r="G11" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="17">
         <f ca="1">ROUND(I11/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
     </row>
     <row r="12" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="15">
         <v>46356</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="15">
         <v>46371</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="17">
         <v>3715</v>
       </c>
-      <c r="F12" s="27">
-        <v>0</v>
-      </c>
-      <c r="G12" s="30">
+      <c r="F12" s="17">
+        <v>0</v>
+      </c>
+      <c r="G12" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="17">
         <f ca="1">ROUND(I12/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="15">
         <v>46295</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="15">
         <v>46351</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="17">
         <f>60*4</f>
         <v>240</v>
       </c>
-      <c r="F13" s="27">
-        <v>0</v>
-      </c>
-      <c r="G13" s="30">
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="17">
         <f ca="1">ROUND(I13/6,0)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="31" t="s">
+      <c r="K13" s="17"/>
+      <c r="L13" s="21" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="15">
         <v>46320</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="15">
         <v>46380</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="17">
         <v>640</v>
       </c>
-      <c r="F14" s="27">
-        <v>0</v>
-      </c>
-      <c r="G14" s="28">
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="17">
         <f ca="1">ROUND(I14/8,0)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="27"/>
-      <c r="L14" s="31" t="s">
+      <c r="K14" s="17"/>
+      <c r="L14" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="15">
         <v>46341</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="15">
         <v>46380</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="17">
         <f>96*4+45+21+25</f>
         <v>475</v>
       </c>
-      <c r="F15" s="27">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
+      <c r="F15" s="17">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="17">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="17">
         <f ca="1">ROUND(I15/9,0)</f>
         <v>0</v>
       </c>
-      <c r="K15" s="27"/>
-      <c r="L15" s="31" t="s">
+      <c r="K15" s="17"/>
+      <c r="L15" s="21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="37" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="32" t="s">
+    <row r="16" spans="1:12" s="27" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-    </row>
-    <row r="17" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="29" t="s">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+    </row>
+    <row r="17" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-    </row>
-    <row r="18" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="40" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="15">
         <v>46308</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="15">
         <v>46315</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="17">
         <v>865</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="17">
         <v>825</v>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="20">
         <f t="shared" ref="G18:G30" si="4">F18/E18</f>
         <v>0.95375722543352603</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="17">
         <f t="shared" ref="H18:H30" si="5">(E18-F18)*G18</f>
         <v>38.150289017341038</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="17">
         <f t="shared" ref="I18:I30" ca="1" si="6">H18/(C18-(IF(B18&gt;TODAY(),B18,TODAY())))</f>
         <v>5.450041288191577</v>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="17">
         <f ca="1">ROUND(I18/1,0)</f>
         <v>5</v>
       </c>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27" t="s">
+      <c r="K18" s="17"/>
+      <c r="L18" s="17" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="40" t="s">
+    <row r="19" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="15">
         <f>C18+1</f>
         <v>46316</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="15">
         <f>C18+8</f>
         <v>46323</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="17">
         <v>1012</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="17">
         <v>896</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="20">
         <f t="shared" si="4"/>
         <v>0.88537549407114624</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="17">
         <f t="shared" si="5"/>
         <v>102.70355731225297</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>14.671936758893281</v>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="17">
         <f ca="1">ROUND(I19/10,0)</f>
         <v>1</v>
       </c>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-    </row>
-    <row r="20" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="40" t="s">
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+    </row>
+    <row r="20" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="15">
         <v>46296</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="15">
         <v>46333</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="17">
         <v>345</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="17">
         <v>27</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="20">
         <f t="shared" si="4"/>
         <v>7.8260869565217397E-2</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="17">
         <f t="shared" si="5"/>
         <v>24.886956521739133</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0.88881987577639765</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="17">
         <f ca="1">ROUND(I20/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="17">
         <v>4</v>
       </c>
-      <c r="L20" s="27" t="s">
+      <c r="L20" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="40" t="s">
+    <row r="21" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="15">
         <f>B20+3</f>
         <v>46299</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="15">
         <f>C20+3</f>
         <v>46336</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="17">
         <v>345</v>
       </c>
-      <c r="F21" s="27">
-        <v>0</v>
-      </c>
-      <c r="G21" s="30">
+      <c r="F21" s="17">
+        <v>0</v>
+      </c>
+      <c r="G21" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="17">
         <f ca="1">ROUND(I21/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-    </row>
-    <row r="22" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="40" t="s">
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="15">
         <v>46305</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="15">
         <f>C21+5</f>
         <v>46341</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="17">
         <f>28*0.96*20.7+13.46*8.4</f>
         <v>669.4799999999999</v>
       </c>
-      <c r="F22" s="27">
-        <v>0</v>
-      </c>
-      <c r="G22" s="30">
+      <c r="F22" s="17">
+        <v>0</v>
+      </c>
+      <c r="G22" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="17">
         <f ca="1">ROUND(I22/5,0)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27" t="s">
+      <c r="K22" s="17"/>
+      <c r="L22" s="17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="40" t="s">
+    <row r="23" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="15">
         <f>C22+1</f>
         <v>46342</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="15">
         <f>B23+4</f>
         <v>46346</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="17">
         <v>1270</v>
       </c>
-      <c r="F23" s="27">
-        <v>0</v>
-      </c>
-      <c r="G23" s="30">
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="17">
         <f ca="1">ROUND(I23/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-    </row>
-    <row r="24" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+    </row>
+    <row r="24" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-    </row>
-    <row r="25" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="40" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="15">
         <v>46297</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="15">
         <v>46318</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="17">
         <f>51/0.115</f>
         <v>443.47826086956519</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="17">
         <v>408</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="20">
         <f t="shared" si="4"/>
         <v>0.92</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="17">
         <f t="shared" si="5"/>
         <v>32.639999999999979</v>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>2.5107692307692293</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="17">
         <f ca="1">ROUND(I25/1,0)</f>
         <v>3</v>
       </c>
-      <c r="K25" s="38">
+      <c r="K25" s="28">
         <v>4</v>
       </c>
-      <c r="L25" s="38"/>
-    </row>
-    <row r="26" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="40" t="s">
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="15">
         <f>B25+1</f>
         <v>46298</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="15">
         <f>C25+8</f>
         <v>46326</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="17">
         <v>780</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="17">
         <v>590</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="20">
         <f t="shared" si="4"/>
         <v>0.75641025641025639</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="17">
         <f t="shared" si="5"/>
         <v>143.7179487179487</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>6.8437118437118425</v>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="17">
         <f ca="1">ROUND(I26/10,0)</f>
         <v>1</v>
       </c>
-      <c r="K26" s="38"/>
-      <c r="L26" s="38"/>
-    </row>
-    <row r="27" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="40" t="s">
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="15">
         <v>46300</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="15">
         <v>46337</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="17">
         <v>215</v>
       </c>
-      <c r="F27" s="38">
+      <c r="F27" s="28">
         <v>78</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="20">
         <f t="shared" si="4"/>
         <v>0.36279069767441863</v>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="17">
         <f t="shared" si="5"/>
         <v>49.70232558139535</v>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>1.5531976744186047</v>
       </c>
-      <c r="J27" s="27">
+      <c r="J27" s="17">
         <f ca="1">ROUND(I27/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27" s="28">
         <v>11</v>
       </c>
-      <c r="L27" s="38"/>
-    </row>
-    <row r="28" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="40" t="s">
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="15">
         <f>B27+3</f>
         <v>46303</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="15">
         <f>C27+3</f>
         <v>46340</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="17">
         <v>215</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="17">
         <v>14</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="20">
         <f t="shared" si="4"/>
         <v>6.5116279069767441E-2</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="17">
         <f t="shared" si="5"/>
         <v>13.088372093023256</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0.37395348837209302</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="17">
         <f ca="1">ROUND(I28/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="28">
         <v>4</v>
       </c>
-      <c r="L28" s="38"/>
-    </row>
-    <row r="29" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="40" t="s">
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="15">
         <v>46311</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="15">
         <f>C28+7</f>
         <v>46347</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="17">
         <f>16*2.05*8.4</f>
         <v>275.52</v>
       </c>
-      <c r="F29" s="27">
-        <v>0</v>
-      </c>
-      <c r="G29" s="30">
+      <c r="F29" s="17">
+        <v>0</v>
+      </c>
+      <c r="G29" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I29" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="J29" s="27">
+      <c r="J29" s="17">
         <f ca="1">ROUND(I29/5,0)</f>
         <v>0</v>
       </c>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-    </row>
-    <row r="30" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="40" t="s">
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="15">
         <f>C29+1</f>
         <v>46348</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="15">
         <f>B30+3</f>
         <v>46351</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="17">
         <v>435</v>
       </c>
-      <c r="F30" s="27">
-        <v>0</v>
-      </c>
-      <c r="G30" s="30">
+      <c r="F30" s="17">
+        <v>0</v>
+      </c>
+      <c r="G30" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H30" s="27">
+      <c r="H30" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I30" s="27">
+      <c r="I30" s="17">
         <f t="shared" ca="1" si="6"/>
         <v>0</v>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="17">
         <f ca="1">ROUND(I30/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K30" s="38"/>
-      <c r="L30" s="38"/>
-    </row>
-    <row r="31" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="29" t="s">
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="38"/>
-      <c r="L31" s="38"/>
-    </row>
-    <row r="32" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="40" t="s">
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="15">
         <v>46299</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="15">
         <v>46325</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="17">
         <v>521</v>
       </c>
-      <c r="F32" s="41">
+      <c r="F32" s="31">
         <v>497</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="20">
         <f t="shared" ref="G32:G44" si="7">F32/E32</f>
         <v>0.95393474088291752</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="17">
         <f t="shared" ref="H32:H44" si="8">(E32-F32)*G32</f>
         <v>22.89443378119002</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="17">
         <f t="shared" ref="I32:I44" ca="1" si="9">H32/(C32-(IF(B32&gt;TODAY(),B32,TODAY())))</f>
         <v>1.1447216890595011</v>
       </c>
-      <c r="J32" s="27">
+      <c r="J32" s="17">
         <f ca="1">ROUND(I32/1,0)</f>
         <v>1</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32" s="28">
         <v>4</v>
       </c>
-      <c r="L32" s="38"/>
-    </row>
-    <row r="33" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="40" t="s">
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="15">
         <f>B32+4</f>
         <v>46303</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="15">
         <f>C32+8</f>
         <v>46333</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="17">
         <v>825</v>
       </c>
-      <c r="F33" s="38">
+      <c r="F33" s="28">
         <v>396</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="20">
         <f t="shared" si="7"/>
         <v>0.48</v>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="17">
         <f t="shared" si="8"/>
         <v>205.92</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>7.3542857142857141</v>
       </c>
-      <c r="J33" s="27">
+      <c r="J33" s="17">
         <f ca="1">ROUND(I33/10,0)</f>
         <v>1</v>
       </c>
-      <c r="K33" s="38">
+      <c r="K33" s="28">
         <v>5</v>
       </c>
-      <c r="L33" s="38"/>
-    </row>
-    <row r="34" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="40" t="s">
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="15">
         <v>46320</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="15">
         <v>46348</v>
       </c>
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="17">
         <v>285</v>
       </c>
-      <c r="F34" s="41">
-        <v>0</v>
-      </c>
-      <c r="G34" s="30">
+      <c r="F34" s="31">
+        <v>0</v>
+      </c>
+      <c r="G34" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J34" s="27">
+      <c r="J34" s="17">
         <f ca="1">ROUND(I34/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-    </row>
-    <row r="35" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="40" t="s">
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="15">
         <f>B34+3</f>
         <v>46323</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="15">
         <f>C34+3</f>
         <v>46351</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="17">
         <f>E34</f>
         <v>285</v>
       </c>
-      <c r="F35" s="41">
-        <v>0</v>
-      </c>
-      <c r="G35" s="30">
+      <c r="F35" s="31">
+        <v>0</v>
+      </c>
+      <c r="G35" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J35" s="27">
+      <c r="J35" s="17">
         <f ca="1">ROUND(I35/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K35" s="38"/>
-      <c r="L35" s="38"/>
-    </row>
-    <row r="36" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="40" t="s">
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="15">
         <v>46311</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="15">
         <f>C35+6</f>
         <v>46357</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="17">
         <v>312</v>
       </c>
-      <c r="F36" s="41">
-        <v>0</v>
-      </c>
-      <c r="G36" s="30">
+      <c r="F36" s="31">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H36" s="27">
+      <c r="H36" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J36" s="27">
+      <c r="J36" s="17">
         <f ca="1">ROUND(I36/5,0)</f>
         <v>0</v>
       </c>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-    </row>
-    <row r="37" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="40" t="s">
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="15">
         <f>C36+1</f>
         <v>46358</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="15">
         <f>B37+3</f>
         <v>46361</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="17">
         <v>456</v>
       </c>
-      <c r="F37" s="41">
-        <v>0</v>
-      </c>
-      <c r="G37" s="30">
+      <c r="F37" s="31">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H37" s="27">
+      <c r="H37" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J37" s="27">
+      <c r="J37" s="17">
         <f ca="1">ROUND(I37/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38"/>
-    </row>
-    <row r="38" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="29" t="s">
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-    </row>
-    <row r="39" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="40" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+    </row>
+    <row r="39" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="15">
         <v>46310</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="15">
         <v>46331</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="17">
         <f>51/0.115</f>
         <v>443.47826086956519</v>
       </c>
-      <c r="F39" s="38">
+      <c r="F39" s="28">
         <v>425.73913043478257</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="20">
         <f t="shared" si="7"/>
         <v>0.96</v>
       </c>
-      <c r="H39" s="27">
+      <c r="H39" s="17">
         <f t="shared" si="8"/>
         <v>17.029565217391319</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0.81093167701863422</v>
       </c>
-      <c r="J39" s="27">
+      <c r="J39" s="17">
         <f ca="1">ROUND(I39/1,0)</f>
         <v>1</v>
       </c>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38" t="s">
+      <c r="K39" s="28"/>
+      <c r="L39" s="28" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="40" t="s">
+    <row r="40" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="15">
         <f>C39+1</f>
         <v>46332</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="15">
         <f>C39+10</f>
         <v>46341</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="17">
         <v>780</v>
       </c>
-      <c r="F40" s="41">
-        <v>0</v>
-      </c>
-      <c r="G40" s="30">
+      <c r="F40" s="31">
+        <v>0</v>
+      </c>
+      <c r="G40" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="17">
         <f ca="1">ROUND(I40/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K40" s="38"/>
-      <c r="L40" s="38"/>
-    </row>
-    <row r="41" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="40" t="s">
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+    </row>
+    <row r="41" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="15">
         <v>46331</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="15">
         <v>46348</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="27">
+      <c r="E41" s="17">
         <v>215</v>
       </c>
-      <c r="F41" s="41">
-        <v>0</v>
-      </c>
-      <c r="G41" s="30">
+      <c r="F41" s="31">
+        <v>0</v>
+      </c>
+      <c r="G41" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H41" s="27">
+      <c r="H41" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J41" s="27">
+      <c r="J41" s="17">
         <f ca="1">ROUND(I41/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="38"/>
-      <c r="L41" s="38"/>
-    </row>
-    <row r="42" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="40" t="s">
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+    </row>
+    <row r="42" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="15">
         <f>B41+3</f>
         <v>46334</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="15">
         <f>C41+7</f>
         <v>46355</v>
       </c>
-      <c r="D42" s="26" t="s">
+      <c r="D42" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="17">
         <v>215</v>
       </c>
-      <c r="F42" s="41">
-        <v>0</v>
-      </c>
-      <c r="G42" s="30">
+      <c r="F42" s="31">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J42" s="27">
+      <c r="J42" s="17">
         <f ca="1">ROUND(I42/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K42" s="38"/>
-      <c r="L42" s="38"/>
-    </row>
-    <row r="43" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="40" t="s">
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+    </row>
+    <row r="43" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="15">
         <v>46342</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="15">
         <f>C42+10</f>
         <v>46365</v>
       </c>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="17">
         <f>16*2.05*8.4</f>
         <v>275.52</v>
       </c>
-      <c r="F43" s="41">
-        <v>0</v>
-      </c>
-      <c r="G43" s="30">
+      <c r="F43" s="31">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J43" s="27">
+      <c r="J43" s="17">
         <f ca="1">ROUND(I43/5,0)</f>
         <v>0</v>
       </c>
-      <c r="K43" s="38"/>
-      <c r="L43" s="38"/>
-    </row>
-    <row r="44" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="40" t="s">
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+    </row>
+    <row r="44" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="25">
+      <c r="B44" s="15">
         <f>C43+1</f>
         <v>46366</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="15">
         <f>B44+5</f>
         <v>46371</v>
       </c>
-      <c r="D44" s="26" t="s">
+      <c r="D44" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="17">
         <v>435</v>
       </c>
-      <c r="F44" s="41">
-        <v>0</v>
-      </c>
-      <c r="G44" s="30">
+      <c r="F44" s="31">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="17">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="J44" s="27">
+      <c r="J44" s="17">
         <f ca="1">ROUND(I44/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K44" s="38"/>
-      <c r="L44" s="38"/>
-    </row>
-    <row r="45" spans="1:12" s="43" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="32" t="s">
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+    </row>
+    <row r="45" spans="1:12" s="33" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-    </row>
-    <row r="46" spans="1:12" s="43" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="32" t="s">
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
+    </row>
+    <row r="46" spans="1:12" s="33" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35"/>
-    </row>
-    <row r="47" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="29" t="s">
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="25"/>
+    </row>
+    <row r="47" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B47" s="15">
         <v>46093</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="15">
         <v>46315</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="17">
         <v>1500</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="17">
         <v>1451</v>
       </c>
-      <c r="G47" s="30">
+      <c r="G47" s="20">
         <f t="shared" ref="G47:G53" si="10">F47/E47</f>
         <v>0.96733333333333338</v>
       </c>
-      <c r="H47" s="27">
+      <c r="H47" s="17">
         <f t="shared" ref="H47:H53" si="11">(E47-F47)*G47</f>
         <v>47.399333333333338</v>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="17">
         <f t="shared" ref="I47:I53" ca="1" si="12">H47/(C47-(IF(B47&gt;TODAY(),B47,TODAY())))</f>
         <v>4.739933333333334</v>
       </c>
-      <c r="J47" s="38">
+      <c r="J47" s="28">
         <f ca="1">ROUND(I47/4,0)</f>
         <v>1</v>
       </c>
-      <c r="K47" s="38">
+      <c r="K47" s="28">
         <v>2</v>
       </c>
-      <c r="L47" s="38"/>
-    </row>
-    <row r="48" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="29" t="s">
+      <c r="L47" s="28"/>
+    </row>
+    <row r="48" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="15">
         <v>46050</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="15">
         <v>46326</v>
       </c>
-      <c r="D48" s="44" t="s">
+      <c r="D48" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="17">
         <f>9830+3200</f>
         <v>13030</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="17">
         <v>10956</v>
       </c>
-      <c r="G48" s="30">
+      <c r="G48" s="20">
         <f t="shared" si="10"/>
         <v>0.84082885648503458</v>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="17">
         <f t="shared" si="11"/>
         <v>1743.8790483499617</v>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="17">
         <f t="shared" ca="1" si="12"/>
         <v>83.04185944523627</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="28">
         <f ca="1">ROUND(I48/12,0)</f>
         <v>7</v>
       </c>
-      <c r="K48" s="38">
+      <c r="K48" s="28">
         <v>4</v>
       </c>
-      <c r="L48" s="38"/>
-    </row>
-    <row r="49" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="29" t="s">
+      <c r="L48" s="28"/>
+    </row>
+    <row r="49" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B49" s="15">
         <v>46002</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="15">
         <v>46322</v>
       </c>
-      <c r="D49" s="44" t="s">
+      <c r="D49" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="17">
         <f>7203</f>
         <v>7203</v>
       </c>
-      <c r="F49" s="27">
+      <c r="F49" s="17">
         <v>6880</v>
       </c>
-      <c r="G49" s="30">
+      <c r="G49" s="20">
         <f t="shared" si="10"/>
         <v>0.95515757323337502</v>
       </c>
-      <c r="H49" s="27">
+      <c r="H49" s="17">
         <f t="shared" si="11"/>
         <v>308.51589615438013</v>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="17">
         <f t="shared" ca="1" si="12"/>
         <v>18.147993891434126</v>
       </c>
-      <c r="J49" s="38">
+      <c r="J49" s="28">
         <f ca="1">ROUND(I49/10,0)</f>
         <v>2</v>
       </c>
-      <c r="K49" s="38">
+      <c r="K49" s="28">
         <v>4</v>
       </c>
-      <c r="L49" s="38"/>
-    </row>
-    <row r="50" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="29" t="s">
+      <c r="L49" s="28"/>
+    </row>
+    <row r="50" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B50" s="15">
         <v>46032</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="15">
         <v>46320</v>
       </c>
-      <c r="D50" s="44" t="s">
+      <c r="D50" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="17">
         <v>9363</v>
       </c>
-      <c r="F50" s="27">
+      <c r="F50" s="17">
         <v>8880</v>
       </c>
-      <c r="G50" s="30">
+      <c r="G50" s="20">
         <f t="shared" si="10"/>
         <v>0.94841396988144822</v>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="17">
         <f t="shared" si="11"/>
         <v>458.08394745273949</v>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="17">
         <f t="shared" ca="1" si="12"/>
         <v>30.538929830182632</v>
       </c>
-      <c r="J50" s="38">
+      <c r="J50" s="28">
         <f ca="1">ROUND(I50/12,0)</f>
         <v>3</v>
       </c>
-      <c r="K50" s="38">
+      <c r="K50" s="28">
         <v>6</v>
       </c>
-      <c r="L50" s="38"/>
-    </row>
-    <row r="51" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="29" t="s">
+      <c r="L50" s="28"/>
+    </row>
+    <row r="51" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B51" s="15">
         <v>46275</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="15">
         <v>46351</v>
       </c>
-      <c r="D51" s="44" t="s">
+      <c r="D51" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="17">
         <f>890+1480+1598+1190</f>
         <v>5158</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51" s="17">
         <v>421</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51" s="20">
         <f t="shared" si="10"/>
         <v>8.1620783249321441E-2</v>
       </c>
-      <c r="H51" s="27">
+      <c r="H51" s="17">
         <f t="shared" si="11"/>
         <v>386.63765025203566</v>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="17">
         <f t="shared" ca="1" si="12"/>
         <v>8.4051663098268623</v>
       </c>
-      <c r="J51" s="38">
+      <c r="J51" s="28">
         <f ca="1">ROUND(I51/9,0)</f>
         <v>1</v>
       </c>
-      <c r="K51" s="38">
-        <v>0</v>
-      </c>
-      <c r="L51" s="38"/>
-    </row>
-    <row r="52" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="29" t="s">
+      <c r="K51" s="28">
+        <v>0</v>
+      </c>
+      <c r="L51" s="28"/>
+    </row>
+    <row r="52" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B52" s="15">
         <v>46275</v>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="15">
         <v>46341</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="17">
         <v>630</v>
       </c>
-      <c r="F52" s="27">
+      <c r="F52" s="17">
         <v>466.2</v>
       </c>
-      <c r="G52" s="30">
+      <c r="G52" s="20">
         <f t="shared" si="10"/>
         <v>0.74</v>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="17">
         <f t="shared" si="11"/>
         <v>121.212</v>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="17">
         <f t="shared" ca="1" si="12"/>
         <v>3.367</v>
       </c>
-      <c r="J52" s="38">
+      <c r="J52" s="28">
         <f ca="1">ROUND(I52/9,0)</f>
         <v>0</v>
       </c>
-      <c r="K52" s="38">
+      <c r="K52" s="28">
         <v>2</v>
       </c>
-      <c r="L52" s="38"/>
-    </row>
-    <row r="53" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="29" t="s">
+      <c r="L52" s="28"/>
+    </row>
+    <row r="53" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="25">
+      <c r="B53" s="15">
         <v>46295</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="15">
         <v>46323</v>
       </c>
-      <c r="D53" s="44" t="s">
+      <c r="D53" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="17">
         <v>3426</v>
       </c>
-      <c r="F53" s="27">
+      <c r="F53" s="17">
         <v>685.2</v>
       </c>
-      <c r="G53" s="30">
+      <c r="G53" s="20">
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="17">
         <f t="shared" si="11"/>
         <v>548.16000000000008</v>
       </c>
-      <c r="I53" s="27">
+      <c r="I53" s="17">
         <f t="shared" ca="1" si="12"/>
         <v>30.453333333333337</v>
       </c>
-      <c r="J53" s="38">
+      <c r="J53" s="28">
         <f ca="1">ROUND(I53/10,0)</f>
         <v>3</v>
       </c>
-      <c r="K53" s="38">
+      <c r="K53" s="28">
         <v>6</v>
       </c>
-      <c r="L53" s="38"/>
-    </row>
-    <row r="54" spans="1:12" s="43" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="32" t="s">
+      <c r="L53" s="28"/>
+    </row>
+    <row r="54" spans="1:12" s="33" customFormat="1" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
-      <c r="L54" s="35"/>
-    </row>
-    <row r="55" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="29" t="s">
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
+    </row>
+    <row r="55" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B55" s="15">
         <v>46252</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="15">
         <v>46346</v>
       </c>
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="17">
         <v>46027</v>
       </c>
-      <c r="F55" s="27">
+      <c r="F55" s="17">
         <v>23692.959999999999</v>
       </c>
-      <c r="G55" s="30">
+      <c r="G55" s="20">
         <f t="shared" ref="G55:G65" si="13">F55/E55</f>
         <v>0.51476220479283896</v>
       </c>
-      <c r="H55" s="27">
+      <c r="H55" s="17">
         <f t="shared" ref="H55:H65" si="14">(E55-F55)*G55</f>
         <v>11496.719672331457</v>
       </c>
-      <c r="I55" s="27">
+      <c r="I55" s="17">
         <f t="shared" ref="I55:I65" ca="1" si="15">H55/(C55-(IF(B55&gt;TODAY(),B55,TODAY())))</f>
         <v>280.4077968861331</v>
       </c>
-      <c r="J55" s="38">
+      <c r="J55" s="28">
         <f ca="1">ROUND(I55/25,0)</f>
         <v>11</v>
       </c>
-      <c r="K55" s="38">
+      <c r="K55" s="28">
         <v>16</v>
       </c>
-      <c r="L55" s="38"/>
-    </row>
-    <row r="56" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="29" t="s">
+      <c r="L55" s="28"/>
+    </row>
+    <row r="56" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="15">
         <v>46213</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="15">
         <v>46354</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="27">
+      <c r="E56" s="17">
         <v>16308</v>
       </c>
-      <c r="F56" s="27">
+      <c r="F56" s="17">
         <v>8643.2400000000016</v>
       </c>
-      <c r="G56" s="30">
+      <c r="G56" s="20">
         <f t="shared" si="13"/>
         <v>0.53000000000000014</v>
       </c>
-      <c r="H56" s="27">
+      <c r="H56" s="17">
         <f t="shared" si="14"/>
         <v>4062.3228000000004</v>
       </c>
-      <c r="I56" s="27">
+      <c r="I56" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>82.904546938775525</v>
       </c>
-      <c r="J56" s="38">
+      <c r="J56" s="28">
         <f ca="1">ROUND(I56/25,0)</f>
         <v>3</v>
       </c>
-      <c r="K56" s="38">
+      <c r="K56" s="28">
         <v>4</v>
       </c>
-      <c r="L56" s="38"/>
-    </row>
-    <row r="57" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="29" t="s">
+      <c r="L56" s="28"/>
+    </row>
+    <row r="57" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B57" s="15">
         <v>46300</v>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="15">
         <v>46326</v>
       </c>
-      <c r="D57" s="44" t="s">
+      <c r="D57" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="17">
         <v>4</v>
       </c>
-      <c r="F57" s="27">
+      <c r="F57" s="17">
         <v>3.6</v>
       </c>
-      <c r="G57" s="30">
+      <c r="G57" s="20">
         <f t="shared" si="13"/>
         <v>0.9</v>
       </c>
-      <c r="H57" s="27">
+      <c r="H57" s="17">
         <f t="shared" si="14"/>
         <v>0.35999999999999993</v>
       </c>
-      <c r="I57" s="27">
+      <c r="I57" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>1.714285714285714E-2</v>
       </c>
-      <c r="J57" s="38">
+      <c r="J57" s="28">
         <f ca="1">ROUND(I57/2,0)</f>
         <v>0</v>
       </c>
-      <c r="K57" s="38">
-        <v>0</v>
-      </c>
-      <c r="L57" s="38"/>
-    </row>
-    <row r="58" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="29" t="s">
+      <c r="K57" s="28">
+        <v>0</v>
+      </c>
+      <c r="L57" s="28"/>
+    </row>
+    <row r="58" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B58" s="15">
         <v>46313</v>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="15">
         <v>46366</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="27">
+      <c r="E58" s="17">
         <v>1517</v>
       </c>
-      <c r="F58" s="27">
+      <c r="F58" s="17">
         <v>174</v>
       </c>
-      <c r="G58" s="30">
+      <c r="G58" s="20">
         <f t="shared" si="13"/>
         <v>0.11470006591957811</v>
       </c>
-      <c r="H58" s="27">
+      <c r="H58" s="17">
         <f t="shared" si="14"/>
         <v>154.04218852999341</v>
       </c>
-      <c r="I58" s="27">
+      <c r="I58" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>2.9064563873583662</v>
       </c>
-      <c r="J58" s="38">
+      <c r="J58" s="28">
         <f ca="1">ROUND(I58/12,0)</f>
         <v>0</v>
       </c>
-      <c r="K58" s="38">
-        <v>0</v>
-      </c>
-      <c r="L58" s="38"/>
-    </row>
-    <row r="59" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="29" t="s">
+      <c r="K58" s="28">
+        <v>0</v>
+      </c>
+      <c r="L58" s="28"/>
+    </row>
+    <row r="59" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B59" s="15">
         <v>46244</v>
       </c>
-      <c r="C59" s="25">
+      <c r="C59" s="15">
         <v>46336</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="17">
         <v>2800</v>
       </c>
-      <c r="F59" s="27">
+      <c r="F59" s="17">
         <v>2735</v>
       </c>
-      <c r="G59" s="30">
+      <c r="G59" s="20">
         <f t="shared" si="13"/>
         <v>0.97678571428571426</v>
       </c>
-      <c r="H59" s="27">
+      <c r="H59" s="17">
         <f t="shared" si="14"/>
         <v>63.491071428571423</v>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>2.0480990783410138</v>
       </c>
-      <c r="J59" s="38">
+      <c r="J59" s="28">
         <f ca="1">ROUND(I59/5,0)</f>
         <v>0</v>
       </c>
-      <c r="K59" s="38">
-        <v>0</v>
-      </c>
-      <c r="L59" s="38"/>
-    </row>
-    <row r="60" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="24" t="s">
+      <c r="K59" s="28">
+        <v>0</v>
+      </c>
+      <c r="L59" s="28"/>
+    </row>
+    <row r="60" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="25">
+      <c r="B60" s="15">
         <v>46253</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="15">
         <v>46354</v>
       </c>
-      <c r="D60" s="44" t="s">
+      <c r="D60" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="27">
+      <c r="E60" s="17">
         <v>45</v>
       </c>
-      <c r="F60" s="27">
+      <c r="F60" s="17">
         <v>43</v>
       </c>
-      <c r="G60" s="30">
+      <c r="G60" s="20">
         <f t="shared" si="13"/>
         <v>0.9555555555555556</v>
       </c>
-      <c r="H60" s="27">
+      <c r="H60" s="17">
         <f t="shared" si="14"/>
         <v>1.9111111111111112</v>
       </c>
-      <c r="I60" s="27">
+      <c r="I60" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>3.9002267573696146E-2</v>
       </c>
-      <c r="J60" s="38">
+      <c r="J60" s="28">
         <f t="shared" ref="J60:J65" ca="1" si="16">ROUND(I60/3,0)</f>
         <v>0</v>
       </c>
-      <c r="K60" s="38">
+      <c r="K60" s="28">
         <v>4</v>
       </c>
-      <c r="L60" s="38"/>
-    </row>
-    <row r="61" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="29" t="s">
+      <c r="L60" s="28"/>
+    </row>
+    <row r="61" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B61" s="15">
         <v>46244</v>
       </c>
-      <c r="C61" s="25">
-        <f>VLOOKUP(A61,[1]OPD!$B$54:$D$76,3,FALSE)</f>
+      <c r="C61" s="15">
+        <f>VLOOKUP(A61,[3]OPD!$B$54:$D$76,3,FALSE)</f>
         <v>46341</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E61" s="27">
+      <c r="E61" s="17">
         <v>65000</v>
       </c>
-      <c r="F61" s="27">
+      <c r="F61" s="17">
         <v>20795</v>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="20">
         <f t="shared" si="13"/>
         <v>0.31992307692307692</v>
       </c>
-      <c r="H61" s="27">
+      <c r="H61" s="17">
         <f t="shared" si="14"/>
         <v>14142.199615384616</v>
       </c>
-      <c r="I61" s="27">
+      <c r="I61" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>392.8388782051282</v>
       </c>
-      <c r="J61" s="38">
+      <c r="J61" s="28">
         <f ca="1">ROUND(I61/60,0)</f>
         <v>7</v>
       </c>
-      <c r="K61" s="38">
+      <c r="K61" s="28">
         <v>8</v>
       </c>
-      <c r="L61" s="38"/>
-    </row>
-    <row r="62" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="29" t="s">
+      <c r="L61" s="28"/>
+    </row>
+    <row r="62" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="25">
+      <c r="B62" s="15">
         <v>46221</v>
       </c>
-      <c r="C62" s="25">
+      <c r="C62" s="15">
         <v>46341</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E62" s="27">
+      <c r="E62" s="17">
         <v>24107</v>
       </c>
-      <c r="F62" s="27">
+      <c r="F62" s="17">
         <v>18928</v>
       </c>
-      <c r="G62" s="30">
+      <c r="G62" s="20">
         <f t="shared" si="13"/>
         <v>0.785166134317833</v>
       </c>
-      <c r="H62" s="27">
+      <c r="H62" s="17">
         <f t="shared" si="14"/>
         <v>4066.3754096320572</v>
       </c>
-      <c r="I62" s="27">
+      <c r="I62" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>112.95487248977936</v>
       </c>
-      <c r="J62" s="38">
+      <c r="J62" s="28">
         <f ca="1">ROUND(I62/60,0)</f>
         <v>2</v>
       </c>
-      <c r="K62" s="38">
+      <c r="K62" s="28">
         <v>4</v>
       </c>
-      <c r="L62" s="38"/>
-    </row>
-    <row r="63" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="29" t="s">
+      <c r="L62" s="28"/>
+    </row>
+    <row r="63" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="25">
+      <c r="B63" s="15">
         <v>46294</v>
       </c>
-      <c r="C63" s="25">
+      <c r="C63" s="15">
         <v>46310</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="D63" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="27">
+      <c r="E63" s="17">
         <v>1</v>
       </c>
-      <c r="F63" s="27">
-        <v>0</v>
-      </c>
-      <c r="G63" s="30">
+      <c r="F63" s="17">
+        <v>0</v>
+      </c>
+      <c r="G63" s="20">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H63" s="27">
+      <c r="H63" s="17">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I63" s="27">
+      <c r="I63" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
-      <c r="J63" s="38">
+      <c r="J63" s="28">
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="K63" s="38">
-        <v>0</v>
-      </c>
-      <c r="L63" s="38"/>
-    </row>
-    <row r="64" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="29" t="s">
+      <c r="K63" s="28">
+        <v>0</v>
+      </c>
+      <c r="L63" s="28"/>
+    </row>
+    <row r="64" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="25">
+      <c r="B64" s="15">
         <v>46294</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="15">
         <v>46346</v>
       </c>
-      <c r="D64" s="44" t="s">
+      <c r="D64" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="27">
+      <c r="E64" s="17">
         <v>12</v>
       </c>
-      <c r="F64" s="27">
+      <c r="F64" s="17">
         <v>6</v>
       </c>
-      <c r="G64" s="30">
+      <c r="G64" s="20">
         <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
-      <c r="H64" s="27">
+      <c r="H64" s="17">
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="I64" s="27">
+      <c r="I64" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>7.3170731707317069E-2</v>
       </c>
-      <c r="J64" s="38">
+      <c r="J64" s="28">
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="K64" s="38">
+      <c r="K64" s="28">
         <v>4</v>
       </c>
-      <c r="L64" s="38"/>
-    </row>
-    <row r="65" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A65" s="29" t="s">
+      <c r="L64" s="28"/>
+    </row>
+    <row r="65" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="25">
+      <c r="B65" s="15">
         <v>46346</v>
       </c>
-      <c r="C65" s="25">
+      <c r="C65" s="15">
         <v>46376</v>
       </c>
-      <c r="D65" s="44" t="s">
+      <c r="D65" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E65" s="27">
+      <c r="E65" s="17">
         <v>1</v>
       </c>
-      <c r="F65" s="27">
+      <c r="F65" s="17">
         <v>0.05</v>
       </c>
-      <c r="G65" s="30">
+      <c r="G65" s="20">
         <f t="shared" si="13"/>
         <v>0.05</v>
       </c>
-      <c r="H65" s="27">
+      <c r="H65" s="17">
         <f t="shared" si="14"/>
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="I65" s="27">
+      <c r="I65" s="17">
         <f t="shared" ca="1" si="15"/>
         <v>1.5833333333333333E-3</v>
       </c>
-      <c r="J65" s="38">
+      <c r="J65" s="28">
         <f t="shared" ca="1" si="16"/>
         <v>0</v>
       </c>
-      <c r="K65" s="38">
-        <v>0</v>
-      </c>
-      <c r="L65" s="38"/>
-    </row>
-    <row r="66" spans="1:12" s="39" customFormat="1" ht="23" x14ac:dyDescent="0.35">
-      <c r="A66" s="19" t="s">
+      <c r="K65" s="28">
+        <v>0</v>
+      </c>
+      <c r="L65" s="28"/>
+    </row>
+    <row r="66" spans="1:12" s="29" customFormat="1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A66" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-      <c r="J66" s="22"/>
-      <c r="K66" s="22"/>
-      <c r="L66" s="22"/>
-    </row>
-    <row r="67" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="29" t="s">
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+    </row>
+    <row r="67" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B67" s="15">
         <v>46305</v>
       </c>
-      <c r="C67" s="25">
+      <c r="C67" s="15">
         <v>46341</v>
       </c>
-      <c r="D67" s="44" t="s">
+      <c r="D67" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E67" s="27">
+      <c r="E67" s="17">
         <v>2250</v>
       </c>
-      <c r="F67" s="38">
+      <c r="F67" s="28">
         <v>202.5</v>
       </c>
-      <c r="G67" s="30">
+      <c r="G67" s="20">
         <f t="shared" ref="G67:G71" si="17">F67/E67</f>
         <v>0.09</v>
       </c>
-      <c r="H67" s="27">
+      <c r="H67" s="17">
         <f t="shared" ref="H67:H71" si="18">(E67-F67)*G67</f>
         <v>184.27500000000001</v>
       </c>
-      <c r="I67" s="27">
+      <c r="I67" s="17">
         <f t="shared" ref="I67:I71" ca="1" si="19">H67/(C67-(IF(B67&gt;TODAY(),B67,TODAY())))</f>
         <v>5.1187500000000004</v>
       </c>
-      <c r="J67" s="38">
+      <c r="J67" s="28">
         <f ca="1">ROUND(I67/10,0)</f>
         <v>1</v>
       </c>
-      <c r="K67" s="38">
+      <c r="K67" s="28">
         <v>7</v>
       </c>
-      <c r="L67" s="38"/>
-    </row>
-    <row r="68" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="29" t="s">
+      <c r="L67" s="28"/>
+    </row>
+    <row r="68" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="25">
+      <c r="B68" s="15">
         <v>46331</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="15">
         <v>46366</v>
       </c>
-      <c r="D68" s="44" t="s">
+      <c r="D68" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="27">
+      <c r="E68" s="17">
         <v>128</v>
       </c>
-      <c r="F68" s="41">
-        <v>0</v>
-      </c>
-      <c r="G68" s="30">
+      <c r="F68" s="31">
+        <v>0</v>
+      </c>
+      <c r="G68" s="20">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H68" s="27">
+      <c r="H68" s="17">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I68" s="27">
+      <c r="I68" s="17">
         <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
-      <c r="J68" s="38">
+      <c r="J68" s="28">
         <f t="shared" ref="J68:J70" ca="1" si="20">ROUND(I68/3,0)</f>
         <v>0</v>
       </c>
-      <c r="K68" s="38">
-        <v>0</v>
-      </c>
-      <c r="L68" s="38"/>
-    </row>
-    <row r="69" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="29" t="s">
+      <c r="K68" s="28">
+        <v>0</v>
+      </c>
+      <c r="L68" s="28"/>
+    </row>
+    <row r="69" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B69" s="15">
         <v>46256</v>
       </c>
-      <c r="C69" s="25">
+      <c r="C69" s="15">
         <v>46351</v>
       </c>
-      <c r="D69" s="26" t="s">
+      <c r="D69" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="27">
+      <c r="E69" s="17">
         <v>1</v>
       </c>
-      <c r="F69" s="38">
+      <c r="F69" s="28">
         <v>0.75</v>
       </c>
-      <c r="G69" s="30">
+      <c r="G69" s="20">
         <f t="shared" si="17"/>
         <v>0.75</v>
       </c>
-      <c r="H69" s="27">
+      <c r="H69" s="17">
         <f t="shared" si="18"/>
         <v>0.1875</v>
       </c>
-      <c r="I69" s="27">
+      <c r="I69" s="17">
         <f t="shared" ca="1" si="19"/>
         <v>4.076086956521739E-3</v>
       </c>
-      <c r="J69" s="38">
+      <c r="J69" s="28">
         <f t="shared" ca="1" si="20"/>
         <v>0</v>
       </c>
-      <c r="K69" s="38">
-        <v>0</v>
-      </c>
-      <c r="L69" s="38"/>
-    </row>
-    <row r="70" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="29" t="s">
+      <c r="K69" s="28">
+        <v>0</v>
+      </c>
+      <c r="L69" s="28"/>
+    </row>
+    <row r="70" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B70" s="15">
         <v>46239</v>
       </c>
-      <c r="C70" s="25">
+      <c r="C70" s="15">
         <v>46361</v>
       </c>
-      <c r="D70" s="26" t="s">
+      <c r="D70" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E70" s="27">
+      <c r="E70" s="17">
         <v>3528</v>
       </c>
-      <c r="F70" s="41">
+      <c r="F70" s="31">
         <v>3528</v>
       </c>
-      <c r="G70" s="30">
+      <c r="G70" s="20">
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
-      <c r="H70" s="27">
+      <c r="H70" s="17">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="I70" s="27">
+      <c r="I70" s="17">
         <f t="shared" ca="1" si="19"/>
         <v>0</v>
       </c>
-      <c r="J70" s="38">
+      <c r="J70" s="28">
         <f t="shared" ca="1" si="20"/>
         <v>0</v>
       </c>
-      <c r="K70" s="38">
+      <c r="K70" s="28">
         <v>2</v>
       </c>
-      <c r="L70" s="38"/>
-    </row>
-    <row r="71" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="29" t="s">
+      <c r="L70" s="28"/>
+    </row>
+    <row r="71" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B71" s="15">
         <v>46295</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="15">
         <v>46326</v>
       </c>
-      <c r="D71" s="26" t="s">
+      <c r="D71" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="27">
+      <c r="E71" s="17">
         <f>29*35</f>
         <v>1015</v>
       </c>
-      <c r="F71" s="38">
+      <c r="F71" s="28">
         <v>659.75</v>
       </c>
-      <c r="G71" s="30">
+      <c r="G71" s="20">
         <f t="shared" si="17"/>
         <v>0.65</v>
       </c>
-      <c r="H71" s="27">
+      <c r="H71" s="17">
         <f t="shared" si="18"/>
         <v>230.91249999999999</v>
       </c>
-      <c r="I71" s="27">
+      <c r="I71" s="17">
         <f t="shared" ca="1" si="19"/>
         <v>10.995833333333334</v>
       </c>
-      <c r="J71" s="38">
+      <c r="J71" s="28">
         <f ca="1">ROUND(I71/10,0)</f>
         <v>1</v>
       </c>
-      <c r="K71" s="38">
+      <c r="K71" s="28">
         <v>2</v>
       </c>
-      <c r="L71" s="38"/>
-    </row>
-    <row r="72" spans="1:12" s="39" customFormat="1" ht="22.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="45" t="s">
+      <c r="L71" s="28"/>
+    </row>
+    <row r="72" spans="1:12" s="29" customFormat="1" ht="22.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="45"/>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
-      <c r="H72" s="45"/>
-      <c r="I72" s="45"/>
-      <c r="J72" s="45"/>
-      <c r="K72" s="45"/>
-      <c r="L72" s="45"/>
-    </row>
-    <row r="73" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="29" t="s">
+      <c r="B72" s="61"/>
+      <c r="C72" s="61"/>
+      <c r="D72" s="61"/>
+      <c r="E72" s="61"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="61"/>
+      <c r="H72" s="61"/>
+      <c r="I72" s="61"/>
+      <c r="J72" s="61"/>
+      <c r="K72" s="61"/>
+      <c r="L72" s="61"/>
+    </row>
+    <row r="73" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="25">
+      <c r="B73" s="15">
         <v>46178</v>
       </c>
-      <c r="C73" s="25">
+      <c r="C73" s="15">
         <v>46233</v>
       </c>
-      <c r="D73" s="44" t="s">
+      <c r="D73" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E73" s="27">
+      <c r="E73" s="17">
         <v>2</v>
       </c>
-      <c r="F73" s="41">
+      <c r="F73" s="31">
         <v>2</v>
       </c>
-      <c r="G73" s="30">
+      <c r="G73" s="20">
         <f t="shared" ref="G73:G76" si="21">F73/E73</f>
         <v>1</v>
       </c>
-      <c r="H73" s="27">
+      <c r="H73" s="17">
         <f t="shared" ref="H73:H76" si="22">(E73-F73)*G73</f>
         <v>0</v>
       </c>
-      <c r="I73" s="30">
+      <c r="I73" s="20">
         <f t="shared" ref="I73:I76" ca="1" si="23">H73/(C73-(IF(B73&gt;TODAY(),B73,TODAY())))</f>
         <v>0</v>
       </c>
-      <c r="J73" s="27">
+      <c r="J73" s="17">
         <f t="shared" ref="J73:J76" ca="1" si="24">ROUND(I73/3,0)</f>
         <v>0</v>
       </c>
-      <c r="K73" s="27">
-        <v>0</v>
-      </c>
-      <c r="L73" s="27"/>
-    </row>
-    <row r="74" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="29" t="s">
+      <c r="K73" s="17">
+        <v>0</v>
+      </c>
+      <c r="L73" s="17"/>
+    </row>
+    <row r="74" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B74" s="15">
         <v>46242</v>
       </c>
-      <c r="C74" s="25">
+      <c r="C74" s="15">
         <v>46320</v>
       </c>
-      <c r="D74" s="44" t="s">
+      <c r="D74" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E74" s="27">
+      <c r="E74" s="17">
         <v>3</v>
       </c>
-      <c r="F74" s="41">
+      <c r="F74" s="31">
         <v>3</v>
       </c>
-      <c r="G74" s="30">
+      <c r="G74" s="20">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="H74" s="27">
+      <c r="H74" s="17">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I74" s="30">
+      <c r="I74" s="20">
         <f t="shared" ca="1" si="23"/>
         <v>0</v>
       </c>
-      <c r="J74" s="27">
+      <c r="J74" s="17">
         <f t="shared" ca="1" si="24"/>
         <v>0</v>
       </c>
-      <c r="K74" s="27">
-        <v>0</v>
-      </c>
-      <c r="L74" s="27"/>
-    </row>
-    <row r="75" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="29" t="s">
+      <c r="K74" s="17">
+        <v>0</v>
+      </c>
+      <c r="L74" s="17"/>
+    </row>
+    <row r="75" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="25">
+      <c r="B75" s="15">
         <v>46306</v>
       </c>
-      <c r="C75" s="25">
+      <c r="C75" s="15">
         <v>46354</v>
       </c>
-      <c r="D75" s="44" t="s">
+      <c r="D75" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E75" s="27">
+      <c r="E75" s="17">
         <v>1</v>
       </c>
-      <c r="F75" s="41">
+      <c r="F75" s="31">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G75" s="30">
+      <c r="G75" s="20">
         <f t="shared" si="21"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="H75" s="27">
+      <c r="H75" s="17">
         <f t="shared" si="22"/>
         <v>0.2475</v>
       </c>
-      <c r="I75" s="30">
+      <c r="I75" s="20">
         <f t="shared" ca="1" si="23"/>
         <v>5.1562500000000002E-3</v>
       </c>
-      <c r="J75" s="27">
+      <c r="J75" s="17">
         <f t="shared" ca="1" si="24"/>
         <v>0</v>
       </c>
-      <c r="K75" s="27">
+      <c r="K75" s="17">
         <v>4</v>
       </c>
-      <c r="L75" s="27"/>
-    </row>
-    <row r="76" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="29" t="s">
+      <c r="L75" s="17"/>
+    </row>
+    <row r="76" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B76" s="25">
+      <c r="B76" s="15">
         <v>46341</v>
       </c>
-      <c r="C76" s="25">
+      <c r="C76" s="15">
         <v>46366</v>
       </c>
-      <c r="D76" s="44" t="s">
+      <c r="D76" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E76" s="27">
+      <c r="E76" s="17">
         <v>1</v>
       </c>
-      <c r="F76" s="41">
-        <v>0</v>
-      </c>
-      <c r="G76" s="30">
+      <c r="F76" s="31">
+        <v>0</v>
+      </c>
+      <c r="G76" s="20">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H76" s="27">
+      <c r="H76" s="17">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I76" s="30">
+      <c r="I76" s="20">
         <f t="shared" ca="1" si="23"/>
         <v>0</v>
       </c>
-      <c r="J76" s="27">
+      <c r="J76" s="17">
         <f t="shared" ca="1" si="24"/>
         <v>0</v>
       </c>
-      <c r="K76" s="27">
+      <c r="K76" s="17">
         <v>2</v>
       </c>
-      <c r="L76" s="27"/>
-    </row>
-    <row r="77" spans="1:12" s="39" customFormat="1" ht="23" x14ac:dyDescent="0.35">
-      <c r="A77" s="19" t="s">
+      <c r="L76" s="17"/>
+    </row>
+    <row r="77" spans="1:12" s="29" customFormat="1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A77" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="22"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="22"/>
-      <c r="L77" s="22"/>
-    </row>
-    <row r="78" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="29" t="s">
+      <c r="B77" s="10"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+    </row>
+    <row r="78" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="25">
+      <c r="B78" s="15">
         <v>46294</v>
       </c>
-      <c r="C78" s="25">
+      <c r="C78" s="15">
         <v>46315</v>
       </c>
-      <c r="D78" s="44"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="27"/>
-      <c r="K78" s="27"/>
-      <c r="L78" s="27"/>
-    </row>
-    <row r="79" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="29" t="s">
+      <c r="D78" s="34"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="31"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+      <c r="L78" s="17"/>
+    </row>
+    <row r="79" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B79" s="15">
         <v>46326</v>
       </c>
-      <c r="C79" s="25">
+      <c r="C79" s="15">
         <v>46346</v>
       </c>
-      <c r="D79" s="44"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="27"/>
-      <c r="K79" s="27"/>
-      <c r="L79" s="27"/>
-    </row>
-    <row r="80" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="29" t="s">
+      <c r="D79" s="34"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+      <c r="L79" s="17"/>
+    </row>
+    <row r="80" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="25">
+      <c r="B80" s="15">
         <v>46323</v>
       </c>
-      <c r="C80" s="25">
+      <c r="C80" s="15">
         <v>46351</v>
       </c>
-      <c r="D80" s="44"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="30"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-    </row>
-    <row r="81" spans="1:12" s="39" customFormat="1" ht="23" x14ac:dyDescent="0.35">
-      <c r="A81" s="19" t="s">
+      <c r="D80" s="34"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
+      <c r="L80" s="17"/>
+    </row>
+    <row r="81" spans="1:12" s="29" customFormat="1" ht="23" x14ac:dyDescent="0.35">
+      <c r="A81" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="22"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="22"/>
-      <c r="I81" s="22"/>
-      <c r="J81" s="22"/>
-      <c r="K81" s="22"/>
-      <c r="L81" s="22"/>
-    </row>
-    <row r="82" spans="1:12" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="29" t="s">
+      <c r="B81" s="10"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="13"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+    </row>
+    <row r="82" spans="1:12" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B82" s="25">
+      <c r="B82" s="15">
         <v>46357</v>
       </c>
-      <c r="C82" s="25">
+      <c r="C82" s="15">
         <v>46380</v>
       </c>
-      <c r="D82" s="44"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="27"/>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17"/>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+      <c r="L82" s="17"/>
     </row>
     <row r="83" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B83" s="25">
+      <c r="B83" s="15">
         <v>46351</v>
       </c>
-      <c r="C83" s="25">
+      <c r="C83" s="15">
         <v>46376</v>
       </c>
-      <c r="D83" s="44"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
-      <c r="J83" s="27"/>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="17"/>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+      <c r="L83" s="17"/>
     </row>
     <row r="84" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="25">
+      <c r="B84" s="15">
         <v>46361</v>
       </c>
-      <c r="C84" s="25">
+      <c r="C84" s="15">
         <v>46380</v>
       </c>
-      <c r="D84" s="44"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="30"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="27"/>
-      <c r="J84" s="27"/>
-      <c r="K84" s="27"/>
-      <c r="L84" s="27"/>
+      <c r="D84" s="34"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="L84" s="17"/>
     </row>
     <row r="85" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B85" s="25">
+      <c r="B85" s="15">
         <v>46346</v>
       </c>
-      <c r="C85" s="25">
+      <c r="C85" s="15">
         <v>46376</v>
       </c>
-      <c r="D85" s="44"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="27"/>
-      <c r="J85" s="27"/>
-      <c r="K85" s="27"/>
-      <c r="L85" s="27"/>
+      <c r="D85" s="34"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="17"/>
+      <c r="I85" s="17"/>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+      <c r="L85" s="17"/>
     </row>
     <row r="1048571" spans="9:9" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="I1048571" s="27">
+      <c r="I1048571" s="17">
         <f ca="1">H1048571/(C1048571-TODAY())</f>
         <v>0</v>
       </c>
@@ -6689,14 +6689,14 @@
   <dimension ref="A1:O1048544"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="37.90625" style="46" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" style="39" customWidth="1"/>
+    <col min="1" max="1" width="37.90625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="29" customWidth="1"/>
     <col min="3" max="4" width="14.54296875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" style="48" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" style="48" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" style="49" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" style="49" customWidth="1"/>
-    <col min="9" max="11" width="14.54296875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" style="37" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" style="37" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="38" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" style="38" customWidth="1"/>
+    <col min="9" max="11" width="14.54296875" style="37" customWidth="1"/>
     <col min="12" max="16384" width="3" style="7"/>
   </cols>
   <sheetData>
@@ -6704,7 +6704,7 @@
       <c r="A1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="50"/>
+      <c r="B1" s="39"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
@@ -6714,2430 +6714,2430 @@
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="51"/>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.35">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="51"/>
-    </row>
-    <row r="3" spans="1:15" s="14" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="40"/>
+    </row>
+    <row r="3" spans="1:15" s="8" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="56" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-    </row>
-    <row r="5" spans="1:15" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="56" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+    </row>
+    <row r="5" spans="1:15" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
     </row>
     <row r="6" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="34">
         <v>45938</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="34">
         <v>46320</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="17">
         <f>4931-703</f>
         <v>4228</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="17">
         <v>4101.16</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="18">
         <f>F6/E6</f>
         <v>0.97</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="17">
         <f>E6-F6</f>
         <v>126.84000000000015</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="17">
         <f ca="1">H6/(C6-(IF(B6&gt;TODAY(),B6,TODAY())))</f>
         <v>8.4560000000000102</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="17">
         <f ca="1">ROUND(I6/1,0)</f>
         <v>8</v>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="34">
         <v>46032</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="34">
         <v>46336</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="17">
         <v>55280</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="17">
         <v>44989</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="18">
         <f t="shared" ref="G7:G16" si="0">F7/E7</f>
         <v>0.81383863965267733</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="17">
         <f>E7-F7</f>
         <v>10291</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="17">
         <f t="shared" ref="I7:I16" ca="1" si="1">H7/(C7-(IF(B7&gt;TODAY(),B7,TODAY())))</f>
         <v>331.96774193548384</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="17">
         <f ca="1">ROUND(I7/12,0)</f>
         <v>28</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="17">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="34">
         <v>46102</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="34">
         <v>46371</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="17">
         <v>782</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="17">
         <v>445.73999999999995</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="18">
         <f t="shared" si="0"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="17">
         <f t="shared" ref="H8:H16" si="2">E8-F8</f>
         <v>336.26000000000005</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>5.0948484848484856</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="17">
         <f ca="1">ROUND(I8/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="34">
         <v>46073</v>
       </c>
-      <c r="C9" s="44">
-        <f>VLOOKUP(A9,[2]EMR!$B$7:$D$131,3,FALSE)</f>
+      <c r="C9" s="34">
+        <f>VLOOKUP(A9,[1]EMR!$B$7:$D$131,3,FALSE)</f>
         <v>46356</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="17">
         <f>17000+7221+1921</f>
         <v>26142</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="17">
         <v>21499.02</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="18">
         <f t="shared" si="0"/>
         <v>0.82239384897865508</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="17">
         <f t="shared" si="2"/>
         <v>4642.9799999999996</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>91.038823529411758</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="17">
         <f ca="1">ROUND(I9/10,0)</f>
         <v>9</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="34">
         <v>46310</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="34">
         <v>46346</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="17">
         <f>4152*1.5</f>
         <v>6228</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="17">
         <v>186.84</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="18">
         <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="17">
         <f t="shared" si="2"/>
         <v>6041.16</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>167.81</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="17">
         <f ca="1">ROUND(I10/12,0)</f>
         <v>14</v>
       </c>
-      <c r="K10" s="27"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
     </row>
     <row r="11" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="34">
         <f>B10+10</f>
         <v>46320</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="34">
         <v>46336</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="17">
         <f>3598*1.5</f>
         <v>5397</v>
       </c>
-      <c r="F11" s="27">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28">
+      <c r="F11" s="17">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="17">
         <f t="shared" si="2"/>
         <v>5397</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>337.3125</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="17">
         <f t="shared" ref="J11:J13" ca="1" si="3">ROUND(I11/12,0)</f>
         <v>28</v>
       </c>
-      <c r="K11" s="27"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
     </row>
     <row r="12" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="34">
         <f>B11+10</f>
         <v>46330</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="34">
         <v>46351</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="17">
         <f>3598*1.5</f>
         <v>5397</v>
       </c>
-      <c r="F12" s="27">
-        <v>0</v>
-      </c>
-      <c r="G12" s="28">
+      <c r="F12" s="17">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="17">
         <f t="shared" si="2"/>
         <v>5397</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>257</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>21</v>
       </c>
-      <c r="K12" s="27"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
     </row>
     <row r="13" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="34">
         <f>B12+10</f>
         <v>46340</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="34">
         <v>46366</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="17">
         <f>3715*1.5</f>
         <v>5572.5</v>
       </c>
-      <c r="F13" s="27">
-        <v>0</v>
-      </c>
-      <c r="G13" s="28">
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="17">
         <f t="shared" si="2"/>
         <v>5572.5</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>214.32692307692307</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="17">
         <f t="shared" ca="1" si="3"/>
         <v>18</v>
       </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
     </row>
     <row r="14" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="44">
+      <c r="B14" s="34">
         <v>46315</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="34">
         <v>46376</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="17">
         <v>290</v>
       </c>
-      <c r="F14" s="27">
-        <v>0</v>
-      </c>
-      <c r="G14" s="28">
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="17">
         <f t="shared" si="2"/>
         <v>290</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>4.7540983606557381</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="17">
         <f ca="1">ROUND(I14/5,0)</f>
         <v>1</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="34">
         <v>46344</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="34">
         <v>46374</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="17">
         <v>530</v>
       </c>
-      <c r="F15" s="27">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
+      <c r="F15" s="17">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="17">
         <f t="shared" si="2"/>
         <v>530</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>17.666666666666668</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="17">
         <f ca="1">ROUND(I15/10,0)</f>
         <v>2</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="34">
         <v>46336</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="34">
         <v>46376</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D16" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="17">
         <v>475</v>
       </c>
-      <c r="F16" s="27">
-        <v>0</v>
-      </c>
-      <c r="G16" s="28">
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="17">
         <f t="shared" si="2"/>
         <v>475</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="17">
         <f t="shared" ca="1" si="1"/>
         <v>11.875</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="17">
         <f ca="1">ROUND(I16/10,0)</f>
         <v>1</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="47"/>
     </row>
     <row r="18" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="34">
         <v>46167</v>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="34">
         <v>46262</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="30">
+      <c r="D19" s="34"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="20">
         <v>1</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="20">
         <v>1</v>
       </c>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
     </row>
     <row r="20" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="34">
         <v>46262</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="34">
         <v>46310</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="30">
+      <c r="D20" s="34"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="20">
         <v>0.54</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="20">
         <f>100%-G20</f>
         <v>0.45999999999999996</v>
       </c>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27">
+      <c r="I20" s="17"/>
+      <c r="J20" s="17">
         <v>4</v>
       </c>
-      <c r="K20" s="27">
+      <c r="K20" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
     </row>
     <row r="22" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="34">
         <v>46193</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="34">
         <v>46298</v>
       </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="30">
+      <c r="D22" s="34"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="20">
         <v>1</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="20">
         <f t="shared" ref="H22:H29" si="4">100%-G22</f>
         <v>0</v>
       </c>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27">
+      <c r="I22" s="17"/>
+      <c r="J22" s="17">
         <v>8</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="34">
         <v>46298</v>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="34">
         <v>46325</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="30">
+      <c r="D23" s="34"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="20">
         <v>0.12</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="20">
         <f t="shared" si="4"/>
         <v>0.88</v>
       </c>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="34">
         <v>46208</v>
       </c>
-      <c r="C25" s="44">
+      <c r="C25" s="34">
         <v>46325</v>
       </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="30">
+      <c r="D25" s="34"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="20">
         <v>0.45</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="20">
         <f t="shared" si="4"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
+      <c r="I25" s="17"/>
+      <c r="J25" s="17">
         <v>10</v>
       </c>
-      <c r="K25" s="27">
+      <c r="K25" s="17">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="61" t="s">
+      <c r="A26" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="44">
+      <c r="B26" s="34">
         <v>46325</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="34">
         <v>46377</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="30">
-        <v>0</v>
-      </c>
-      <c r="H26" s="30">
+      <c r="D26" s="34"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="20">
+        <v>0</v>
+      </c>
+      <c r="H26" s="20">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
     </row>
     <row r="27" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="56" t="s">
+      <c r="A27" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
     </row>
     <row r="28" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="61" t="s">
+      <c r="A28" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="44">
+      <c r="B28" s="34">
         <v>46213</v>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="34">
         <v>46264</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="30">
+      <c r="D28" s="34"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="20">
         <v>1</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="20">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I28" s="27" t="s">
+      <c r="I28" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="J28" s="27" t="s">
+      <c r="J28" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="K28" s="27"/>
+      <c r="K28" s="17"/>
     </row>
     <row r="29" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="61" t="s">
+      <c r="A29" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="34">
         <v>46266</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="34">
         <v>46351</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="30">
+      <c r="D29" s="34"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="20">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="20">
         <f t="shared" si="4"/>
         <v>0.42000000000000004</v>
       </c>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
     </row>
     <row r="31" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="44">
+      <c r="B31" s="34">
         <v>46280</v>
       </c>
-      <c r="C31" s="44">
+      <c r="C31" s="34">
         <v>46325</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="17">
         <v>340</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="17">
         <v>129.19999999999999</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="20">
         <f>F31/E31</f>
         <v>0.37999999999999995</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31" s="28">
         <f>E31-F31</f>
         <v>210.8</v>
       </c>
-      <c r="I31" s="27">
+      <c r="I31" s="17">
         <f t="shared" ref="I31:I40" ca="1" si="5">H31/(C31-(IF(B31&gt;TODAY(),B31,TODAY())))</f>
         <v>10.540000000000001</v>
       </c>
-      <c r="J31" s="27">
+      <c r="J31" s="17">
         <f ca="1">ROUND(I31/4,0)</f>
         <v>3</v>
       </c>
-      <c r="K31" s="27">
+      <c r="K31" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="44">
+      <c r="B32" s="34">
         <v>46290</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="34">
         <v>46327</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="17">
         <v>350</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="17">
         <v>147</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="20">
         <f t="shared" ref="G32:G40" si="6">F32/E32</f>
         <v>0.42</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="28">
         <f>E32-F32</f>
         <v>203</v>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>9.2272727272727266</v>
       </c>
-      <c r="J32" s="27">
+      <c r="J32" s="17">
         <f ca="1">ROUND(I32/3,0)</f>
         <v>3</v>
       </c>
-      <c r="K32" s="27">
+      <c r="K32" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="34">
         <v>46272</v>
       </c>
-      <c r="C33" s="44">
+      <c r="C33" s="34">
         <v>46325</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="17">
         <v>3754</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="17">
         <v>2552.7200000000003</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="20">
         <f t="shared" si="6"/>
         <v>0.68</v>
       </c>
-      <c r="H33" s="38">
+      <c r="H33" s="28">
         <f>E33-F33</f>
         <v>1201.2799999999997</v>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>60.063999999999986</v>
       </c>
-      <c r="J33" s="27">
+      <c r="J33" s="17">
         <f ca="1">ROUND(I33/10,0)</f>
         <v>6</v>
       </c>
-      <c r="K33" s="27">
+      <c r="K33" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="44">
+      <c r="B34" s="34">
         <v>46300</v>
       </c>
-      <c r="C34" s="44">
+      <c r="C34" s="34">
         <v>46320</v>
       </c>
-      <c r="D34" s="44" t="s">
+      <c r="D34" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="17">
         <f>29*30.5</f>
         <v>884.5</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="17">
         <v>610.30499999999995</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="20">
         <f t="shared" si="6"/>
         <v>0.69</v>
       </c>
-      <c r="H34" s="38">
+      <c r="H34" s="28">
         <f>E34-F34</f>
         <v>274.19500000000005</v>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>18.279666666666671</v>
       </c>
-      <c r="J34" s="27">
+      <c r="J34" s="17">
         <v>2</v>
       </c>
-      <c r="K34" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="56" t="s">
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="57"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
     </row>
     <row r="36" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="44">
+      <c r="B36" s="34">
         <v>46239</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="34">
         <v>46366</v>
       </c>
-      <c r="D36" s="44" t="s">
+      <c r="D36" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="17">
         <v>935</v>
       </c>
-      <c r="F36" s="27">
+      <c r="F36" s="17">
         <v>392.7</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="20">
         <f t="shared" si="6"/>
         <v>0.42</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36" s="28">
         <f t="shared" ref="H36:H40" si="7">E36-F36</f>
         <v>542.29999999999995</v>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>8.8901639344262282</v>
       </c>
-      <c r="J36" s="27">
+      <c r="J36" s="17">
         <f ca="1">ROUND(I36/3,0)</f>
         <v>3</v>
       </c>
-      <c r="K36" s="27">
+      <c r="K36" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="44">
+      <c r="B37" s="34">
         <v>46252</v>
       </c>
-      <c r="C37" s="44">
+      <c r="C37" s="34">
         <v>46368</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="D37" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="17">
         <v>490</v>
       </c>
-      <c r="F37" s="27">
+      <c r="F37" s="17">
         <v>68.600000000000009</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="20">
         <f t="shared" si="6"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="H37" s="38">
+      <c r="H37" s="28">
         <f t="shared" si="7"/>
         <v>421.4</v>
       </c>
-      <c r="I37" s="27">
+      <c r="I37" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>6.6888888888888882</v>
       </c>
-      <c r="J37" s="27">
+      <c r="J37" s="17">
         <f t="shared" ref="J37" ca="1" si="8">ROUND(I37/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K37" s="27">
+      <c r="K37" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="29" t="s">
+    <row r="38" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="44">
+      <c r="B38" s="34">
         <v>46270</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="34">
         <v>46374</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D38" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="17">
         <v>564</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="17">
         <v>112.80000000000001</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="20">
         <f t="shared" si="6"/>
         <v>0.2</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="28">
         <f t="shared" si="7"/>
         <v>451.2</v>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>6.5391304347826082</v>
       </c>
-      <c r="J38" s="27">
+      <c r="J38" s="17">
         <f ca="1">ROUND(I38/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K38" s="27">
+      <c r="K38" s="17">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="29" t="s">
+    <row r="39" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="44">
+      <c r="B39" s="34">
         <v>46244</v>
       </c>
-      <c r="C39" s="44">
+      <c r="C39" s="34">
         <v>46366</v>
       </c>
-      <c r="D39" s="44" t="s">
+      <c r="D39" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="17">
         <v>485</v>
       </c>
-      <c r="F39" s="27">
+      <c r="F39" s="17">
         <v>82.45</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="20">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39" s="28">
         <f t="shared" si="7"/>
         <v>402.55</v>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>6.5991803278688526</v>
       </c>
-      <c r="J39" s="27">
+      <c r="J39" s="17">
         <f ca="1">ROUND(I39/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K39" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="29" t="s">
+      <c r="K39" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="44">
+      <c r="B40" s="34">
         <v>46267</v>
       </c>
-      <c r="C40" s="44">
+      <c r="C40" s="34">
         <v>46356</v>
       </c>
-      <c r="D40" s="44" t="s">
+      <c r="D40" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="17">
         <f>(70.6+77.6+70.6)*2</f>
         <v>437.59999999999997</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40" s="17">
         <v>126.90399999999998</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="20">
         <f t="shared" si="6"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="H40" s="38">
+      <c r="H40" s="28">
         <f t="shared" si="7"/>
         <v>310.69599999999997</v>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="17">
         <f t="shared" ca="1" si="5"/>
         <v>6.0920784313725482</v>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="17">
         <f ca="1">ROUND(I40/3,0)</f>
         <v>2</v>
       </c>
-      <c r="K40" s="27">
+      <c r="K40" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="39" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A41" s="56" t="s">
+    <row r="41" spans="1:11" s="29" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A41" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-    </row>
-    <row r="42" spans="1:11" s="39" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A42" s="56" t="s">
+      <c r="B41" s="46"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="47"/>
+      <c r="K41" s="47"/>
+    </row>
+    <row r="42" spans="1:11" s="29" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A42" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="58"/>
-    </row>
-    <row r="43" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="29" t="s">
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+    </row>
+    <row r="43" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="44">
+      <c r="B43" s="34">
         <v>46034</v>
       </c>
-      <c r="C43" s="44">
+      <c r="C43" s="34">
         <v>46275</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D43" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="17">
         <v>1537</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="17">
         <v>1537</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="20">
         <f t="shared" ref="G43:G60" si="9">F43/E43</f>
         <v>1</v>
       </c>
-      <c r="H43" s="38">
+      <c r="H43" s="28">
         <f t="shared" ref="H43:H49" si="10">E43-F43</f>
         <v>0</v>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="17">
         <f t="shared" ref="I43:I49" ca="1" si="11">H43/(C43-(IF(B43&gt;TODAY(),B43,TODAY())))</f>
         <v>0</v>
       </c>
-      <c r="J43" s="38">
+      <c r="J43" s="28">
         <f ca="1">ROUND(I43/4,0)</f>
         <v>0</v>
       </c>
-      <c r="K43" s="27">
+      <c r="K43" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="44">
+      <c r="B44" s="34">
         <v>46049</v>
       </c>
-      <c r="C44" s="44">
+      <c r="C44" s="34">
         <v>46366</v>
       </c>
-      <c r="D44" s="44" t="s">
+      <c r="D44" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="17">
         <f>2760+1800</f>
         <v>4560</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="17">
         <v>3242.4</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44" s="20">
         <f t="shared" si="9"/>
         <v>0.71105263157894738</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="28">
         <f t="shared" si="10"/>
         <v>1317.6</v>
       </c>
-      <c r="I44" s="27">
+      <c r="I44" s="17">
         <f t="shared" ca="1" si="11"/>
         <v>21.599999999999998</v>
       </c>
-      <c r="J44" s="38">
+      <c r="J44" s="28">
         <f t="shared" ref="J44:J60" ca="1" si="12">ROUND(I44/4,0)</f>
         <v>5</v>
       </c>
-      <c r="K44" s="27">
+      <c r="K44" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="44">
+      <c r="B45" s="34">
         <v>46042</v>
       </c>
-      <c r="C45" s="44">
+      <c r="C45" s="34">
         <v>46326</v>
       </c>
-      <c r="D45" s="44" t="s">
+      <c r="D45" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="17">
         <v>9830</v>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="17">
         <v>9633.4</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45" s="20">
         <f t="shared" si="9"/>
         <v>0.98</v>
       </c>
-      <c r="H45" s="38">
+      <c r="H45" s="28">
         <f t="shared" si="10"/>
         <v>196.60000000000036</v>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="17">
         <f t="shared" ca="1" si="11"/>
         <v>9.3619047619047784</v>
       </c>
-      <c r="J45" s="38">
+      <c r="J45" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>2</v>
       </c>
-      <c r="K45" s="27">
+      <c r="K45" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="44">
+      <c r="B46" s="34">
         <v>46032</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="34">
         <v>46358</v>
       </c>
-      <c r="D46" s="44" t="s">
+      <c r="D46" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="17">
         <v>8425</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="17">
         <v>5863.25</v>
       </c>
-      <c r="G46" s="30">
+      <c r="G46" s="20">
         <f t="shared" si="9"/>
         <v>0.69593471810089025</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H46" s="28">
         <f t="shared" si="10"/>
         <v>2561.75</v>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="17">
         <f t="shared" ca="1" si="11"/>
         <v>48.334905660377359</v>
       </c>
-      <c r="J46" s="38">
+      <c r="J46" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>12</v>
       </c>
-      <c r="K46" s="27">
+      <c r="K46" s="17">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="29" t="s">
+    <row r="47" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="44">
+      <c r="B47" s="34">
         <v>46275</v>
       </c>
-      <c r="C47" s="44">
+      <c r="C47" s="34">
         <v>46374</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="17">
         <v>8263</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="17">
         <v>2523.12</v>
       </c>
-      <c r="G47" s="30">
+      <c r="G47" s="20">
         <f t="shared" si="9"/>
         <v>0.30535156722739926</v>
       </c>
-      <c r="H47" s="38">
+      <c r="H47" s="28">
         <f t="shared" si="10"/>
         <v>5739.88</v>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="17">
         <f t="shared" ca="1" si="11"/>
         <v>83.186666666666667</v>
       </c>
-      <c r="J47" s="38">
+      <c r="J47" s="28">
         <f ca="1">ROUND(I47/4,0)</f>
         <v>21</v>
       </c>
-      <c r="K47" s="27">
+      <c r="K47" s="17">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="29" t="s">
+    <row r="48" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="44">
+      <c r="B48" s="34">
         <v>46305</v>
       </c>
-      <c r="C48" s="44">
+      <c r="C48" s="34">
         <v>46361</v>
       </c>
-      <c r="D48" s="44" t="s">
+      <c r="D48" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="17">
         <v>820</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="17">
         <v>32.799999999999997</v>
       </c>
-      <c r="G48" s="30">
+      <c r="G48" s="20">
         <f t="shared" si="9"/>
         <v>3.9999999999999994E-2</v>
       </c>
-      <c r="H48" s="38">
+      <c r="H48" s="28">
         <f t="shared" si="10"/>
         <v>787.2</v>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="17">
         <f t="shared" ca="1" si="11"/>
         <v>14.057142857142859</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>4</v>
       </c>
-      <c r="K48" s="27">
+      <c r="K48" s="17">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="29" t="s">
+    <row r="49" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="44">
+      <c r="B49" s="34">
         <v>46327</v>
       </c>
-      <c r="C49" s="44">
+      <c r="C49" s="34">
         <v>46361</v>
       </c>
-      <c r="D49" s="44" t="s">
+      <c r="D49" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="17">
         <v>3121</v>
       </c>
-      <c r="F49" s="27">
-        <v>0</v>
-      </c>
-      <c r="G49" s="30">
+      <c r="F49" s="17">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H49" s="38">
+      <c r="H49" s="28">
         <f t="shared" si="10"/>
         <v>3121</v>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="17">
         <f t="shared" ca="1" si="11"/>
         <v>91.794117647058826</v>
       </c>
-      <c r="J49" s="38">
+      <c r="J49" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>23</v>
       </c>
-      <c r="K49" s="27">
+      <c r="K49" s="17">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="39" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A50" s="56" t="s">
+    <row r="50" spans="1:11" s="29" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A50" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="58"/>
-      <c r="K50" s="58"/>
-    </row>
-    <row r="51" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="29" t="s">
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+    </row>
+    <row r="51" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="44">
+      <c r="B51" s="34">
         <v>46268</v>
       </c>
-      <c r="C51" s="44">
+      <c r="C51" s="34">
         <v>46353</v>
       </c>
-      <c r="D51" s="44" t="s">
+      <c r="D51" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="17">
         <v>58034</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51" s="17">
         <v>12767.48</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51" s="20">
         <f t="shared" si="9"/>
         <v>0.22</v>
       </c>
-      <c r="H51" s="38">
+      <c r="H51" s="28">
         <f t="shared" ref="H51:H64" si="13">E51-F51</f>
         <v>45266.520000000004</v>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="17">
         <f t="shared" ref="I51:I64" ca="1" si="14">H51/(C51-(IF(B51&gt;TODAY(),B51,TODAY())))</f>
         <v>943.05250000000012</v>
       </c>
-      <c r="J51" s="38">
+      <c r="J51" s="28">
         <v>27</v>
       </c>
-      <c r="K51" s="27">
+      <c r="K51" s="17">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="29" t="s">
+    <row r="52" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="44">
+      <c r="B52" s="34">
         <v>46270</v>
       </c>
-      <c r="C52" s="44">
+      <c r="C52" s="34">
         <v>46347</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="17">
         <v>23078</v>
       </c>
-      <c r="F52" s="27">
+      <c r="F52" s="17">
         <v>9773.86</v>
       </c>
-      <c r="G52" s="30">
+      <c r="G52" s="20">
         <f t="shared" si="9"/>
         <v>0.42351416933876423</v>
       </c>
-      <c r="H52" s="38">
+      <c r="H52" s="28">
         <f t="shared" si="13"/>
         <v>13304.14</v>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>316.76523809523809</v>
       </c>
-      <c r="J52" s="38">
+      <c r="J52" s="28">
         <v>23</v>
       </c>
-      <c r="K52" s="27">
+      <c r="K52" s="17">
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="29" t="s">
+    <row r="53" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="44">
+      <c r="B53" s="34">
         <v>46361</v>
       </c>
-      <c r="C53" s="44">
+      <c r="C53" s="34">
         <v>46376</v>
       </c>
-      <c r="D53" s="44" t="s">
+      <c r="D53" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="17">
         <v>4</v>
       </c>
-      <c r="F53" s="27">
-        <v>0</v>
-      </c>
-      <c r="G53" s="30">
+      <c r="F53" s="17">
+        <v>0</v>
+      </c>
+      <c r="G53" s="20">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H53" s="38">
+      <c r="H53" s="28">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="I53" s="27">
+      <c r="I53" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>0.26666666666666666</v>
       </c>
-      <c r="J53" s="38">
+      <c r="J53" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="K53" s="27">
+      <c r="K53" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="44">
+      <c r="B54" s="34">
         <v>46230</v>
       </c>
-      <c r="C54" s="44">
+      <c r="C54" s="34">
         <v>46365</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="D54" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="17">
         <v>2943</v>
       </c>
-      <c r="F54" s="27">
+      <c r="F54" s="17">
         <v>1500.93</v>
       </c>
-      <c r="G54" s="30">
+      <c r="G54" s="20">
         <f t="shared" si="9"/>
         <v>0.51</v>
       </c>
-      <c r="H54" s="38">
+      <c r="H54" s="28">
         <f t="shared" si="13"/>
         <v>1442.07</v>
       </c>
-      <c r="I54" s="27">
+      <c r="I54" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>24.034499999999998</v>
       </c>
-      <c r="J54" s="38">
+      <c r="J54" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>6</v>
       </c>
-      <c r="K54" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="29" t="s">
+      <c r="K54" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="44">
+      <c r="B55" s="34">
         <v>46230</v>
       </c>
-      <c r="C55" s="44">
+      <c r="C55" s="34">
         <v>46365</v>
       </c>
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="17">
         <v>48</v>
       </c>
-      <c r="F55" s="27">
+      <c r="F55" s="17">
         <v>14</v>
       </c>
-      <c r="G55" s="30">
+      <c r="G55" s="20">
         <f t="shared" si="9"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="H55" s="38">
+      <c r="H55" s="28">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
-      <c r="I55" s="27">
+      <c r="I55" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>0.56666666666666665</v>
       </c>
-      <c r="J55" s="38">
+      <c r="J55" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="K55" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" s="39" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="29" t="s">
+      <c r="K55" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" s="29" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="44">
+      <c r="B56" s="34">
         <v>46189</v>
       </c>
-      <c r="C56" s="44">
+      <c r="C56" s="34">
         <v>46364</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="27">
+      <c r="E56" s="17">
         <v>58362</v>
       </c>
-      <c r="F56" s="27">
+      <c r="F56" s="17">
         <v>28013.759999999998</v>
       </c>
-      <c r="G56" s="30">
+      <c r="G56" s="20">
         <f t="shared" si="9"/>
         <v>0.48</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="28">
         <f t="shared" si="13"/>
         <v>30348.240000000002</v>
       </c>
-      <c r="I56" s="27">
+      <c r="I56" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>514.37694915254235</v>
       </c>
-      <c r="J56" s="38">
+      <c r="J56" s="28">
         <v>22</v>
       </c>
-      <c r="K56" s="27">
+      <c r="K56" s="17">
         <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="44">
+      <c r="B57" s="34">
         <v>46189</v>
       </c>
-      <c r="C57" s="44">
+      <c r="C57" s="34">
         <v>46353</v>
       </c>
-      <c r="D57" s="44" t="s">
+      <c r="D57" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E57" s="27">
+      <c r="E57" s="17">
         <f>21280+4620</f>
         <v>25900</v>
       </c>
-      <c r="F57" s="27">
+      <c r="F57" s="17">
         <v>16317</v>
       </c>
-      <c r="G57" s="30">
+      <c r="G57" s="20">
         <f t="shared" si="9"/>
         <v>0.63</v>
       </c>
-      <c r="H57" s="38">
+      <c r="H57" s="28">
         <f t="shared" si="13"/>
         <v>9583</v>
       </c>
-      <c r="I57" s="27">
+      <c r="I57" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>199.64583333333334</v>
       </c>
-      <c r="J57" s="38">
+      <c r="J57" s="28">
         <v>18</v>
       </c>
-      <c r="K57" s="27">
+      <c r="K57" s="17">
         <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="44">
+      <c r="B58" s="34">
         <v>46305</v>
       </c>
-      <c r="C58" s="44">
+      <c r="C58" s="34">
         <v>46321</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="27">
+      <c r="E58" s="17">
         <v>1</v>
       </c>
-      <c r="F58" s="27">
-        <v>0</v>
-      </c>
-      <c r="G58" s="30">
+      <c r="F58" s="17">
+        <v>0</v>
+      </c>
+      <c r="G58" s="20">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H58" s="38">
+      <c r="H58" s="28">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="I58" s="27">
+      <c r="I58" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>6.25E-2</v>
       </c>
-      <c r="J58" s="38">
+      <c r="J58" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="K58" s="27">
+      <c r="K58" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B59" s="44">
+      <c r="B59" s="34">
         <v>46310</v>
       </c>
-      <c r="C59" s="44">
+      <c r="C59" s="34">
         <v>46367</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="17">
         <v>14</v>
       </c>
-      <c r="F59" s="27">
-        <v>0</v>
-      </c>
-      <c r="G59" s="30">
+      <c r="F59" s="17">
+        <v>0</v>
+      </c>
+      <c r="G59" s="20">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H59" s="38">
+      <c r="H59" s="28">
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>0.24561403508771928</v>
       </c>
-      <c r="J59" s="38">
+      <c r="J59" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="K59" s="27">
+      <c r="K59" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B60" s="44">
+      <c r="B60" s="34">
         <v>46346</v>
       </c>
-      <c r="C60" s="44">
+      <c r="C60" s="34">
         <v>46366</v>
       </c>
-      <c r="D60" s="44" t="s">
+      <c r="D60" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="E60" s="27">
+      <c r="E60" s="17">
         <v>1</v>
       </c>
-      <c r="F60" s="27">
-        <v>0</v>
-      </c>
-      <c r="G60" s="30">
+      <c r="F60" s="17">
+        <v>0</v>
+      </c>
+      <c r="G60" s="20">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H60" s="38">
+      <c r="H60" s="28">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="I60" s="27">
+      <c r="I60" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>0.05</v>
       </c>
-      <c r="J60" s="38">
+      <c r="J60" s="28">
         <f t="shared" ca="1" si="12"/>
         <v>0</v>
       </c>
-      <c r="K60" s="27">
+      <c r="K60" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A61" s="56" t="s">
+      <c r="A61" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="59"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="58"/>
-      <c r="J61" s="58"/>
-      <c r="K61" s="58"/>
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="47"/>
+      <c r="J61" s="47"/>
+      <c r="K61" s="47"/>
     </row>
     <row r="62" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="B62" s="44">
+      <c r="B62" s="34">
         <v>46310</v>
       </c>
-      <c r="C62" s="44">
+      <c r="C62" s="34">
         <v>46351</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E62" s="27">
+      <c r="E62" s="17">
         <v>2250</v>
       </c>
-      <c r="F62" s="27">
+      <c r="F62" s="17">
         <v>1012.5</v>
       </c>
-      <c r="G62" s="30">
+      <c r="G62" s="20">
         <v>0.45</v>
       </c>
-      <c r="H62" s="38">
+      <c r="H62" s="28">
         <f t="shared" si="13"/>
         <v>1237.5</v>
       </c>
-      <c r="I62" s="27">
+      <c r="I62" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>30.182926829268293</v>
       </c>
-      <c r="J62" s="38">
+      <c r="J62" s="28">
         <f ca="1">ROUND(I62/10,0)</f>
         <v>3</v>
       </c>
-      <c r="K62" s="27">
+      <c r="K62" s="17">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B63" s="44">
+      <c r="B63" s="34">
         <v>46310</v>
       </c>
-      <c r="C63" s="44">
+      <c r="C63" s="34">
         <v>46347</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="D63" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E63" s="27">
+      <c r="E63" s="17">
         <v>756</v>
       </c>
-      <c r="F63" s="27">
+      <c r="F63" s="17">
         <v>756</v>
       </c>
-      <c r="G63" s="30">
+      <c r="G63" s="20">
         <v>1</v>
       </c>
-      <c r="H63" s="38">
+      <c r="H63" s="28">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I63" s="27">
+      <c r="I63" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
-      <c r="J63" s="38">
+      <c r="J63" s="28">
         <f t="shared" ref="J63:J64" ca="1" si="15">ROUND(I63/10,0)</f>
         <v>0</v>
       </c>
-      <c r="K63" s="27">
+      <c r="K63" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="44">
+      <c r="B64" s="34">
         <v>46331</v>
       </c>
-      <c r="C64" s="44">
+      <c r="C64" s="34">
         <v>46372</v>
       </c>
-      <c r="D64" s="44" t="s">
+      <c r="D64" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="27">
+      <c r="E64" s="17">
         <v>128</v>
       </c>
-      <c r="F64" s="27">
-        <v>0</v>
-      </c>
-      <c r="G64" s="30">
-        <v>0</v>
-      </c>
-      <c r="H64" s="38">
+      <c r="F64" s="17">
+        <v>0</v>
+      </c>
+      <c r="G64" s="20">
+        <v>0</v>
+      </c>
+      <c r="H64" s="28">
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="I64" s="27">
+      <c r="I64" s="17">
         <f t="shared" ca="1" si="14"/>
         <v>3.1219512195121952</v>
       </c>
-      <c r="J64" s="38">
+      <c r="J64" s="28">
         <f t="shared" ca="1" si="15"/>
         <v>0</v>
       </c>
-      <c r="K64" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A65" s="56" t="s">
+      <c r="K64" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="B65" s="57"/>
-      <c r="C65" s="57"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="58"/>
-      <c r="K65" s="58"/>
+      <c r="B65" s="46"/>
+      <c r="C65" s="46"/>
+      <c r="D65" s="46"/>
+      <c r="E65" s="47"/>
+      <c r="F65" s="47"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="47"/>
+      <c r="J65" s="47"/>
+      <c r="K65" s="47"/>
     </row>
     <row r="66" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B66" s="44">
+      <c r="B66" s="34">
         <v>46295</v>
       </c>
-      <c r="C66" s="44">
+      <c r="C66" s="34">
         <v>46331</v>
       </c>
-      <c r="D66" s="44" t="s">
+      <c r="D66" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="27">
+      <c r="E66" s="17">
         <v>2</v>
       </c>
-      <c r="F66" s="27"/>
-      <c r="G66" s="30">
+      <c r="F66" s="17"/>
+      <c r="G66" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H66" s="30">
+      <c r="H66" s="20">
         <f>100%-G66</f>
         <v>0.92999999999999994</v>
       </c>
-      <c r="I66" s="30">
+      <c r="I66" s="20">
         <f ca="1">(1-H66)*E66/(C66-(IF(B66&gt;TODAY(),B66,TODAY())))</f>
         <v>5.3846153846153896E-3</v>
       </c>
-      <c r="J66" s="27">
+      <c r="J66" s="17">
         <v>4</v>
       </c>
-      <c r="K66" s="27">
+      <c r="K66" s="17">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B67" s="44">
+      <c r="B67" s="34">
         <v>46302</v>
       </c>
-      <c r="C67" s="44">
+      <c r="C67" s="34">
         <v>46344</v>
       </c>
-      <c r="D67" s="44" t="s">
+      <c r="D67" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E67" s="27">
+      <c r="E67" s="17">
         <v>1</v>
       </c>
-      <c r="F67" s="27"/>
-      <c r="G67" s="30">
-        <v>0</v>
-      </c>
-      <c r="H67" s="30">
+      <c r="F67" s="17"/>
+      <c r="G67" s="20">
+        <v>0</v>
+      </c>
+      <c r="H67" s="20">
         <f t="shared" ref="H67:H71" si="16">100%-G67</f>
         <v>1</v>
       </c>
-      <c r="I67" s="30">
+      <c r="I67" s="20">
         <f t="shared" ref="I67:I71" ca="1" si="17">(1-H67)*E67/(C67-(IF(B67&gt;TODAY(),B67,TODAY())))</f>
         <v>0</v>
       </c>
-      <c r="J67" s="27">
-        <v>0</v>
-      </c>
-      <c r="K67" s="27"/>
+      <c r="J67" s="17">
+        <v>0</v>
+      </c>
+      <c r="K67" s="17"/>
     </row>
     <row r="68" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B68" s="44">
+      <c r="B68" s="34">
         <v>46306</v>
       </c>
-      <c r="C68" s="44">
+      <c r="C68" s="34">
         <v>46354</v>
       </c>
-      <c r="D68" s="44" t="s">
+      <c r="D68" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E68" s="27">
+      <c r="E68" s="17">
         <v>2</v>
       </c>
-      <c r="F68" s="27"/>
-      <c r="G68" s="30">
-        <v>0</v>
-      </c>
-      <c r="H68" s="30">
+      <c r="F68" s="17"/>
+      <c r="G68" s="20">
+        <v>0</v>
+      </c>
+      <c r="H68" s="20">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="I68" s="30">
+      <c r="I68" s="20">
         <f t="shared" ca="1" si="17"/>
         <v>0</v>
       </c>
-      <c r="J68" s="27">
-        <v>0</v>
-      </c>
-      <c r="K68" s="27"/>
+      <c r="J68" s="17">
+        <v>0</v>
+      </c>
+      <c r="K68" s="17"/>
     </row>
     <row r="69" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B69" s="44">
+      <c r="B69" s="34">
         <v>46341</v>
       </c>
-      <c r="C69" s="44">
+      <c r="C69" s="34">
         <v>46377</v>
       </c>
-      <c r="D69" s="44" t="s">
+      <c r="D69" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E69" s="27">
+      <c r="E69" s="17">
         <v>2</v>
       </c>
-      <c r="F69" s="27"/>
-      <c r="G69" s="30">
-        <v>0</v>
-      </c>
-      <c r="H69" s="30">
+      <c r="F69" s="17"/>
+      <c r="G69" s="20">
+        <v>0</v>
+      </c>
+      <c r="H69" s="20">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="I69" s="30">
+      <c r="I69" s="20">
         <f t="shared" ca="1" si="17"/>
         <v>0</v>
       </c>
-      <c r="J69" s="27">
-        <v>0</v>
-      </c>
-      <c r="K69" s="27"/>
+      <c r="J69" s="17">
+        <v>0</v>
+      </c>
+      <c r="K69" s="17"/>
     </row>
     <row r="70" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B70" s="44">
+      <c r="B70" s="34">
         <v>46319</v>
       </c>
-      <c r="C70" s="44">
+      <c r="C70" s="34">
         <f>B70+45</f>
         <v>46364</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="D70" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="27">
+      <c r="E70" s="17">
         <v>2</v>
       </c>
-      <c r="F70" s="27"/>
-      <c r="G70" s="30">
-        <v>0</v>
-      </c>
-      <c r="H70" s="30">
+      <c r="F70" s="17"/>
+      <c r="G70" s="20">
+        <v>0</v>
+      </c>
+      <c r="H70" s="20">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="I70" s="30">
+      <c r="I70" s="20">
         <f t="shared" ca="1" si="17"/>
         <v>0</v>
       </c>
-      <c r="J70" s="27">
-        <v>0</v>
-      </c>
-      <c r="K70" s="27"/>
+      <c r="J70" s="17">
+        <v>0</v>
+      </c>
+      <c r="K70" s="17"/>
     </row>
     <row r="71" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B71" s="44">
+      <c r="B71" s="34">
         <v>46323</v>
       </c>
-      <c r="C71" s="44">
+      <c r="C71" s="34">
         <f>B71+50</f>
         <v>46373</v>
       </c>
-      <c r="D71" s="44" t="s">
+      <c r="D71" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="27">
+      <c r="E71" s="17">
         <v>2</v>
       </c>
-      <c r="F71" s="27"/>
-      <c r="G71" s="30">
-        <v>0</v>
-      </c>
-      <c r="H71" s="30">
+      <c r="F71" s="17"/>
+      <c r="G71" s="20">
+        <v>0</v>
+      </c>
+      <c r="H71" s="20">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="I71" s="30">
+      <c r="I71" s="20">
         <f t="shared" ca="1" si="17"/>
         <v>0</v>
       </c>
-      <c r="J71" s="27">
-        <v>0</v>
-      </c>
-      <c r="K71" s="27"/>
-    </row>
-    <row r="72" spans="1:11" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="56" t="s">
+      <c r="J71" s="17">
+        <v>0</v>
+      </c>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="57"/>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="59"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="58"/>
-      <c r="J72" s="58"/>
-      <c r="K72" s="58"/>
+      <c r="B72" s="46"/>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="47"/>
+      <c r="F72" s="47"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="47"/>
+      <c r="J72" s="47"/>
+      <c r="K72" s="47"/>
     </row>
     <row r="73" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="29" t="s">
+      <c r="A73" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="44">
+      <c r="B73" s="34">
         <v>46275</v>
       </c>
-      <c r="C73" s="44">
+      <c r="C73" s="34">
         <v>46303</v>
       </c>
-      <c r="D73" s="44"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
-      <c r="K73" s="27"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
     </row>
     <row r="74" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="29" t="s">
+      <c r="A74" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B74" s="44">
+      <c r="B74" s="34">
         <v>46320</v>
       </c>
-      <c r="C74" s="44">
+      <c r="C74" s="34">
         <v>46336</v>
       </c>
-      <c r="D74" s="44"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="27"/>
-      <c r="K74" s="27"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+      <c r="K74" s="17"/>
     </row>
     <row r="75" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B75" s="44">
+      <c r="B75" s="34">
         <v>46323</v>
       </c>
-      <c r="C75" s="44">
+      <c r="C75" s="34">
         <v>46341</v>
       </c>
-      <c r="D75" s="44"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="27"/>
-      <c r="J75" s="27"/>
-      <c r="K75" s="27"/>
-    </row>
-    <row r="76" spans="1:11" s="60" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="62" t="s">
+      <c r="D75" s="34"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:11" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="B76" s="63"/>
-      <c r="C76" s="63"/>
-      <c r="D76" s="63"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="65"/>
-      <c r="H76" s="65"/>
-      <c r="I76" s="64"/>
-      <c r="J76" s="64"/>
-      <c r="K76" s="64"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="53"/>
+      <c r="K76" s="53"/>
     </row>
     <row r="77" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="29" t="s">
+      <c r="A77" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="B77" s="44">
+      <c r="B77" s="34">
         <v>46357</v>
       </c>
-      <c r="C77" s="44">
+      <c r="C77" s="34">
         <v>46380</v>
       </c>
-      <c r="D77" s="44"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="27"/>
-      <c r="J77" s="27"/>
-      <c r="K77" s="27"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
     </row>
     <row r="78" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B78" s="44">
+      <c r="B78" s="34">
         <v>46351</v>
       </c>
-      <c r="C78" s="44">
+      <c r="C78" s="34">
         <v>46376</v>
       </c>
-      <c r="D78" s="44"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="27"/>
-      <c r="K78" s="27"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
     </row>
     <row r="79" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="29" t="s">
+      <c r="A79" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="44">
+      <c r="B79" s="34">
         <v>46361</v>
       </c>
-      <c r="C79" s="44">
+      <c r="C79" s="34">
         <v>46380</v>
       </c>
-      <c r="D79" s="44"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="27"/>
-      <c r="K79" s="27"/>
+      <c r="D79" s="34"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
     </row>
     <row r="80" spans="1:11" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="44">
+      <c r="B80" s="34">
         <v>46346</v>
       </c>
-      <c r="C80" s="44">
+      <c r="C80" s="34">
         <v>46376</v>
       </c>
-      <c r="D80" s="44"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="30"/>
-      <c r="H80" s="30"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="17"/>
+      <c r="K80" s="17"/>
     </row>
     <row r="1048544" spans="7:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="G1048544" s="30" t="e">
-        <f>VLOOKUP(A1048544,'[3]EMR - Activity wise'!$A$7:$E$83,5,FALSE)</f>
+      <c r="G1048544" s="20" t="e">
+        <f>VLOOKUP(A1048544,'[2]EMR - Activity wise'!$A$7:$E$83,5,FALSE)</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select a period to highlight in H2. A Chart legend is in J2 to AI2" sqref="A2:H2 K2" xr:uid="{CA81BC9F-70CA-4E0B-9DE7-267A3AEFB0A2}"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\OneDrive\Desktop\AIIMS REWARI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Legion\OneDrive\Documents\GitHub\daily-progress-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFBC2F0-927A-4861-8DDA-E46D52E12B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BAC27D-EDC9-45F2-A777-E67C36D20A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{0D064328-DC67-411D-BEE3-DF99AB8C76F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="OPD Backup" sheetId="1" r:id="rId1"/>
-    <sheet name="EMR Backup" sheetId="2" r:id="rId2"/>
+    <sheet name="OPD BACKUP" sheetId="1" r:id="rId1"/>
+    <sheet name="EMR BACKUP" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -891,10 +891,10 @@
     <xf numFmtId="9" fontId="21" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -903,10 +903,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="6" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3775,28 +3775,28 @@
       <c r="D2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="56" t="s">
+      <c r="H2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="56" t="s">
+      <c r="K2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="56" t="s">
+      <c r="L2" s="59" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3805,14 +3805,14 @@
       <c r="B3" s="64"/>
       <c r="C3" s="64"/>
       <c r="D3" s="65"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="56"/>
       <c r="F3" s="62"/>
       <c r="G3" s="62"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="59"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
@@ -6743,25 +6743,25 @@
       <c r="D3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="56" t="s">
+      <c r="K3" s="59" t="s">
         <v>92</v>
       </c>
     </row>
@@ -6770,13 +6770,13 @@
       <c r="B4" s="58"/>
       <c r="C4" s="58"/>
       <c r="D4" s="58"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:15" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A5" s="45" t="s">
@@ -9127,17 +9127,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select a period to highlight in H2. A Chart legend is in J2 to AI2" sqref="A2:H2 K2" xr:uid="{CA81BC9F-70CA-4E0B-9DE7-267A3AEFB0A2}"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -3,47 +3,47 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D877BB78-0B59-4F35-8527-08EFF21AA40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECDA190-E19E-4E0C-AAD0-C597BFF9A41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="764" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="OPD  Backup Sheet" sheetId="20" r:id="rId1"/>
-    <sheet name="EMR Backup Sheet" sheetId="21" r:id="rId2"/>
+    <sheet name="OPD BACKUP" sheetId="20" r:id="rId1"/>
+    <sheet name="EMR BACKUP" sheetId="21" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="Actual" localSheetId="1">('EMR Backup Sheet'!PeriodInActual*('EMR Backup Sheet'!#REF!&gt;0))*'EMR Backup Sheet'!PeriodInPlan</definedName>
-    <definedName name="Actual" localSheetId="0">('OPD  Backup Sheet'!PeriodInActual*('OPD  Backup Sheet'!#REF!&gt;0))*'OPD  Backup Sheet'!PeriodInPlan</definedName>
+    <definedName name="Actual" localSheetId="1">('EMR BACKUP'!PeriodInActual*('EMR BACKUP'!#REF!&gt;0))*'EMR BACKUP'!PeriodInPlan</definedName>
+    <definedName name="Actual" localSheetId="0">('OPD BACKUP'!PeriodInActual*('OPD BACKUP'!#REF!&gt;0))*'OPD BACKUP'!PeriodInPlan</definedName>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
-    <definedName name="ActualBeyond" localSheetId="1">'EMR Backup Sheet'!PeriodInActual*('EMR Backup Sheet'!#REF!&gt;0)</definedName>
-    <definedName name="ActualBeyond" localSheetId="0">'OPD  Backup Sheet'!PeriodInActual*('OPD  Backup Sheet'!#REF!&gt;0)</definedName>
+    <definedName name="ActualBeyond" localSheetId="1">'EMR BACKUP'!PeriodInActual*('EMR BACKUP'!#REF!&gt;0)</definedName>
+    <definedName name="ActualBeyond" localSheetId="0">'OPD BACKUP'!PeriodInActual*('OPD BACKUP'!#REF!&gt;0)</definedName>
     <definedName name="ActualBeyond">PeriodInActual*(#REF!&gt;0)</definedName>
-    <definedName name="PercentComplete" localSheetId="1">'EMR Backup Sheet'!PercentCompleteBeyond*'EMR Backup Sheet'!PeriodInPlan</definedName>
-    <definedName name="PercentComplete" localSheetId="0">'OPD  Backup Sheet'!PercentCompleteBeyond*'OPD  Backup Sheet'!PeriodInPlan</definedName>
+    <definedName name="PercentComplete" localSheetId="1">'EMR BACKUP'!PercentCompleteBeyond*'EMR BACKUP'!PeriodInPlan</definedName>
+    <definedName name="PercentComplete" localSheetId="0">'OPD BACKUP'!PercentCompleteBeyond*'OPD BACKUP'!PeriodInPlan</definedName>
     <definedName name="PercentComplete">PercentCompleteBeyond*PeriodInPlan</definedName>
-    <definedName name="PercentCompleteBeyond" localSheetId="1">('EMR Backup Sheet'!A$4=MEDIAN('EMR Backup Sheet'!A$4,'EMR Backup Sheet'!#REF!,'EMR Backup Sheet'!#REF!+'EMR Backup Sheet'!#REF!)*('EMR Backup Sheet'!#REF!&gt;0))*(('EMR Backup Sheet'!A$4&lt;(INT('EMR Backup Sheet'!#REF!+'EMR Backup Sheet'!#REF!*'EMR Backup Sheet'!#REF!)))+('EMR Backup Sheet'!A$4='EMR Backup Sheet'!#REF!))*('EMR Backup Sheet'!#REF!&gt;0)</definedName>
-    <definedName name="PercentCompleteBeyond" localSheetId="0">('OPD  Backup Sheet'!A$3=MEDIAN('OPD  Backup Sheet'!A$3,'OPD  Backup Sheet'!#REF!,'OPD  Backup Sheet'!#REF!+'OPD  Backup Sheet'!#REF!)*('OPD  Backup Sheet'!#REF!&gt;0))*(('OPD  Backup Sheet'!A$3&lt;(INT('OPD  Backup Sheet'!#REF!+'OPD  Backup Sheet'!#REF!*'OPD  Backup Sheet'!#REF!)))+('OPD  Backup Sheet'!A$3='OPD  Backup Sheet'!#REF!))*('OPD  Backup Sheet'!#REF!&gt;0)</definedName>
+    <definedName name="PercentCompleteBeyond" localSheetId="1">('EMR BACKUP'!A$4=MEDIAN('EMR BACKUP'!A$4,'EMR BACKUP'!#REF!,'EMR BACKUP'!#REF!+'EMR BACKUP'!#REF!)*('EMR BACKUP'!#REF!&gt;0))*(('EMR BACKUP'!A$4&lt;(INT('EMR BACKUP'!#REF!+'EMR BACKUP'!#REF!*'EMR BACKUP'!#REF!)))+('EMR BACKUP'!A$4='EMR BACKUP'!#REF!))*('EMR BACKUP'!#REF!&gt;0)</definedName>
+    <definedName name="PercentCompleteBeyond" localSheetId="0">('OPD BACKUP'!A$3=MEDIAN('OPD BACKUP'!A$3,'OPD BACKUP'!#REF!,'OPD BACKUP'!#REF!+'OPD BACKUP'!#REF!)*('OPD BACKUP'!#REF!&gt;0))*(('OPD BACKUP'!A$3&lt;(INT('OPD BACKUP'!#REF!+'OPD BACKUP'!#REF!*'OPD BACKUP'!#REF!)))+('OPD BACKUP'!A$3='OPD BACKUP'!#REF!))*('OPD BACKUP'!#REF!&gt;0)</definedName>
     <definedName name="PercentCompleteBeyond">(#REF!=MEDIAN(#REF!,#REF!,#REF!+#REF!)*(#REF!&gt;0))*((#REF!&lt;(INT(#REF!+#REF!*#REF!)))+(#REF!=#REF!))*(#REF!&gt;0)</definedName>
-    <definedName name="period_selected" localSheetId="1">'EMR Backup Sheet'!#REF!</definedName>
-    <definedName name="period_selected" localSheetId="0">'OPD  Backup Sheet'!#REF!</definedName>
+    <definedName name="period_selected" localSheetId="1">'EMR BACKUP'!#REF!</definedName>
+    <definedName name="period_selected" localSheetId="0">'OPD BACKUP'!#REF!</definedName>
     <definedName name="period_selected">#REF!</definedName>
-    <definedName name="PeriodInActual" localSheetId="1">'EMR Backup Sheet'!A$4=MEDIAN('EMR Backup Sheet'!A$4,'EMR Backup Sheet'!#REF!,'EMR Backup Sheet'!#REF!+'EMR Backup Sheet'!#REF!-1)</definedName>
-    <definedName name="PeriodInActual" localSheetId="0">'OPD  Backup Sheet'!A$3=MEDIAN('OPD  Backup Sheet'!A$3,'OPD  Backup Sheet'!#REF!,'OPD  Backup Sheet'!#REF!+'OPD  Backup Sheet'!#REF!-1)</definedName>
+    <definedName name="PeriodInActual" localSheetId="1">'EMR BACKUP'!A$4=MEDIAN('EMR BACKUP'!A$4,'EMR BACKUP'!#REF!,'EMR BACKUP'!#REF!+'EMR BACKUP'!#REF!-1)</definedName>
+    <definedName name="PeriodInActual" localSheetId="0">'OPD BACKUP'!A$3=MEDIAN('OPD BACKUP'!A$3,'OPD BACKUP'!#REF!,'OPD BACKUP'!#REF!+'OPD BACKUP'!#REF!-1)</definedName>
     <definedName name="PeriodInActual">#REF!=MEDIAN(#REF!,#REF!,#REF!+#REF!-1)</definedName>
-    <definedName name="PeriodInPlan" localSheetId="1">'EMR Backup Sheet'!A$4=MEDIAN('EMR Backup Sheet'!A$4,'EMR Backup Sheet'!$B1,'EMR Backup Sheet'!$B1+'EMR Backup Sheet'!#REF!-1)</definedName>
-    <definedName name="PeriodInPlan" localSheetId="0">'OPD  Backup Sheet'!A$3=MEDIAN('OPD  Backup Sheet'!A$3,'OPD  Backup Sheet'!$B1,'OPD  Backup Sheet'!$B1+'OPD  Backup Sheet'!#REF!-1)</definedName>
+    <definedName name="PeriodInPlan" localSheetId="1">'EMR BACKUP'!A$4=MEDIAN('EMR BACKUP'!A$4,'EMR BACKUP'!$B1,'EMR BACKUP'!$B1+'EMR BACKUP'!#REF!-1)</definedName>
+    <definedName name="PeriodInPlan" localSheetId="0">'OPD BACKUP'!A$3=MEDIAN('OPD BACKUP'!A$3,'OPD BACKUP'!$B1,'OPD BACKUP'!$B1+'OPD BACKUP'!#REF!-1)</definedName>
     <definedName name="PeriodInPlan">#REF!=MEDIAN(#REF!,#REF!,#REF!+#REF!-1)</definedName>
-    <definedName name="Plan" localSheetId="1">'EMR Backup Sheet'!PeriodInPlan*('EMR Backup Sheet'!$B1&gt;0)</definedName>
-    <definedName name="Plan" localSheetId="0">'OPD  Backup Sheet'!PeriodInPlan*('OPD  Backup Sheet'!$B1&gt;0)</definedName>
+    <definedName name="Plan" localSheetId="1">'EMR BACKUP'!PeriodInPlan*('EMR BACKUP'!$B1&gt;0)</definedName>
+    <definedName name="Plan" localSheetId="0">'OPD BACKUP'!PeriodInPlan*('OPD BACKUP'!$B1&gt;0)</definedName>
     <definedName name="Plan">PeriodInPlan*(#REF!&gt;0)</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'EMR Backup Sheet'!$3:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'OPD  Backup Sheet'!$2:$3</definedName>
-    <definedName name="TitleRegion..BO60" localSheetId="1">'EMR Backup Sheet'!$A$3:$A$4</definedName>
-    <definedName name="TitleRegion..BO60" localSheetId="0">'OPD  Backup Sheet'!$A$2:$A$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'EMR BACKUP'!$3:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'OPD BACKUP'!$2:$3</definedName>
+    <definedName name="TitleRegion..BO60" localSheetId="1">'EMR BACKUP'!$A$3:$A$4</definedName>
+    <definedName name="TitleRegion..BO60" localSheetId="0">'OPD BACKUP'!$A$2:$A$3</definedName>
     <definedName name="TitleRegion..BO60">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -424,10 +424,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-14009]d/m/yy;@"/>
-    <numFmt numFmtId="167" formatCode="[$-14009]dd/mm/yy;@"/>
-    <numFmt numFmtId="168" formatCode="[$-409]dd\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-14009]d/m/yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-14009]dd/mm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -927,88 +927,88 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="12" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="6" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="8" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="9" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="9" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="8" borderId="9" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="0" borderId="9" xfId="22" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="12" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="6" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="8" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="9" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="9" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="8" borderId="9" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="0" borderId="9" xfId="22" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="22" applyFont="1" applyAlignment="1">
@@ -1029,7 +1029,7 @@
     <xf numFmtId="9" fontId="14" fillId="8" borderId="9" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1065,37 +1065,37 @@
     <xf numFmtId="9" fontId="20" fillId="8" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="9" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="10" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="10" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="7" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="10" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="10" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="10" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1153,614 +1153,221 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="EMR"/>
+      <sheetName val="Sheet1"/>
       <sheetName val="OPD"/>
-      <sheetName val="IPD"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Brickwork</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D7">
-            <v>46320</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Plaster</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D8">
-            <v>46336</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Ground Floor</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D9">
-            <v>46325</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>1st Floor</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D10">
-            <v>46315</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>2nd Floor</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D11">
-            <v>46310</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>3rd Floor</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D12">
-            <v>46310</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>Above terrace</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D13">
-            <v>46336</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Aluminum Joineries</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D14">
-            <v>46371</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Fire door frame &amp; shutter</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D15">
-            <v>46371</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Flooring &amp; dado</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D16">
-            <v>46356</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>False Ceiling</v>
-          </cell>
-          <cell r="C17">
-            <v>46310</v>
-          </cell>
-          <cell r="D17">
-            <v>46370</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Ground Floor</v>
-          </cell>
-          <cell r="C18">
-            <v>46310</v>
-          </cell>
-          <cell r="D18">
-            <v>46325</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>1st Floor</v>
-          </cell>
-          <cell r="C19">
-            <v>46325</v>
-          </cell>
-          <cell r="D19">
-            <v>46340</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>2nd Floor</v>
-          </cell>
-          <cell r="C20">
-            <v>46340</v>
-          </cell>
-          <cell r="D20">
-            <v>46355</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>3rd Floor</v>
-          </cell>
-          <cell r="C21">
-            <v>46355</v>
-          </cell>
-          <cell r="D21">
-            <v>46370</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Lift facia granite</v>
-          </cell>
-          <cell r="C22">
-            <v>46315</v>
-          </cell>
-          <cell r="D22">
-            <v>46350</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v xml:space="preserve">Courtyard Plaster </v>
-          </cell>
-          <cell r="C23">
-            <v>46293</v>
-          </cell>
-          <cell r="D23">
-            <v>46325</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>SS Handrail</v>
-          </cell>
-          <cell r="C24">
-            <v>46336</v>
-          </cell>
-          <cell r="D24">
-            <v>46372</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Over Terrace</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>OHT&amp;Mummty</v>
-          </cell>
-          <cell r="C26">
-            <v>46290</v>
-          </cell>
-          <cell r="D26">
-            <v>46310</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>OHT Waterproofing &amp; Tiling</v>
-          </cell>
-          <cell r="C27">
-            <v>46315</v>
-          </cell>
-          <cell r="D27">
-            <v>46327</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>LMR</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D28">
-            <v>46311</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>Terrace Waterproofing&amp;HRT Tiles</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D29">
-            <v>46320</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>Pedestals</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D30">
-            <v>46325</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>Polycarbonate Sheet</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D31">
-            <v>46320</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>External</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Shaft brickwork &amp; plaster</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Elevation A</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D34">
-            <v>46320</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Elevation B</v>
-          </cell>
-          <cell r="C35">
-            <v>46295</v>
-          </cell>
-          <cell r="D35">
-            <v>46326</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>Elevation C</v>
-          </cell>
-          <cell r="C36">
-            <v>46283</v>
-          </cell>
-          <cell r="D36">
-            <v>46295</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>Elevation D</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D37">
-            <v>46305</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>External Stone Cladding</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>Elevation A</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>Elevation B</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>Elevation C</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>Elevation D</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>Structural Glazing</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="str">
-            <v>Elevation A</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>Elevation B</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>Elevation C</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>Elevation D</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="str">
-            <v>MEP</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="str">
-            <v>Frist Fix</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="str">
-            <v>Electrical</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="str">
-            <v>Wall Conduit &amp; GI Box Fixing</v>
-          </cell>
-          <cell r="C51" t="str">
-            <v xml:space="preserve">Completed </v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="str">
-            <v>Cable Tray Installation</v>
-          </cell>
-          <cell r="C52" t="str">
-            <v xml:space="preserve">Completed </v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="str">
-            <v>DB Installation</v>
-          </cell>
-          <cell r="C53" t="str">
-            <v xml:space="preserve">Completed </v>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>OPD Balance Activities Schedule (11-Sep-2026)</v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
-            <v>PHE</v>
+            <v>Electrical</v>
           </cell>
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>CI Pipiing</v>
+            <v>Wiring</v>
           </cell>
           <cell r="C55" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D55">
-            <v>46366</v>
+            <v>46325</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>CPVC Piping</v>
+            <v>Cable Laying &amp; Panel Installation</v>
           </cell>
           <cell r="C56" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D56">
-            <v>46366</v>
+            <v>46325</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
-            <v>GI Piping</v>
-          </cell>
-          <cell r="C57" t="str">
-            <v>WIP</v>
+            <v>UPS Installation</v>
+          </cell>
+          <cell r="C57">
+            <v>46291</v>
           </cell>
           <cell r="D57">
-            <v>46366</v>
+            <v>46305</v>
           </cell>
         </row>
         <row r="58">
           <cell r="B58" t="str">
-            <v>HVAC</v>
+            <v>DB Dresssing</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D58">
+            <v>46336</v>
           </cell>
         </row>
         <row r="59">
           <cell r="B59" t="str">
-            <v>Ducting &amp; Insulation</v>
-          </cell>
-          <cell r="C59" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D59">
-            <v>46326</v>
+            <v>PHE</v>
           </cell>
         </row>
         <row r="60">
           <cell r="B60" t="str">
-            <v>Piping installation</v>
+            <v>Cister&amp; Sensor Fixing</v>
           </cell>
           <cell r="C60" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D60">
-            <v>46326</v>
+            <v>46288</v>
           </cell>
         </row>
         <row r="61">
           <cell r="B61" t="str">
-            <v>AHU Installation</v>
-          </cell>
-          <cell r="C61" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D61">
-            <v>46326</v>
+            <v>HVAC</v>
           </cell>
         </row>
         <row r="62">
           <cell r="B62" t="str">
-            <v>Firefighting</v>
+            <v>Duct testinfg &amp; dropper for diffusere</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D62">
+            <v>46366</v>
           </cell>
         </row>
         <row r="63">
           <cell r="B63" t="str">
-            <v>Piping installation</v>
+            <v>Pipe Testing</v>
           </cell>
           <cell r="C63" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D63">
-            <v>46358</v>
+            <v>46310</v>
           </cell>
         </row>
         <row r="64">
           <cell r="B64" t="str">
-            <v>ELV</v>
+            <v>AHU Connection</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D64">
+            <v>46311</v>
           </cell>
         </row>
         <row r="65">
           <cell r="B65" t="str">
-            <v>PVC conduiting &amp; GI box fixing</v>
-          </cell>
-          <cell r="C65" t="str">
-            <v xml:space="preserve">Completed </v>
+            <v>Firefighting</v>
           </cell>
         </row>
         <row r="66">
           <cell r="B66" t="str">
-            <v>Raceway Installation</v>
+            <v>Sprinkler Flexible connection &amp; testing</v>
           </cell>
           <cell r="C66" t="str">
-            <v xml:space="preserve">Completed </v>
+            <v>WIP</v>
+          </cell>
+          <cell r="D66">
+            <v>46340</v>
           </cell>
         </row>
         <row r="67">
           <cell r="B67" t="str">
-            <v>MGPS</v>
+            <v>Wet Riser &amp; FHC installation</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D67">
+            <v>46319</v>
           </cell>
         </row>
         <row r="68">
           <cell r="B68" t="str">
-            <v>Copper Pipning</v>
+            <v>ELV</v>
           </cell>
         </row>
         <row r="69">
           <cell r="B69" t="str">
-            <v>PTTS</v>
+            <v>CAT 6 cabling</v>
           </cell>
           <cell r="C69" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D69">
-            <v>46366</v>
+            <v>46341</v>
           </cell>
         </row>
         <row r="70">
           <cell r="B70" t="str">
-            <v>Pipe Installation</v>
+            <v>PA &amp; FAS cabling</v>
           </cell>
           <cell r="C70" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D70">
-            <v>46366</v>
+            <v>46341</v>
           </cell>
         </row>
         <row r="71">
           <cell r="B71" t="str">
-            <v>Second Fix</v>
+            <v>Fire Panel Installation</v>
+          </cell>
+          <cell r="C71">
+            <v>46291</v>
+          </cell>
+          <cell r="D71">
+            <v>46295</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72" t="str">
-            <v>Electrical</v>
+            <v>Network Switch Installation &amp; connection</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D72">
+            <v>46346</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73" t="str">
-            <v>Wiring</v>
-          </cell>
-          <cell r="C73" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D73">
-            <v>46386</v>
+            <v>MGPS</v>
           </cell>
         </row>
         <row r="74">
           <cell r="B74" t="str">
-            <v>Cable Laying &amp; Panel Installation</v>
-          </cell>
-          <cell r="C74" t="str">
-            <v>WIP</v>
+            <v>Copper Pipe testing</v>
+          </cell>
+          <cell r="C74">
+            <v>46310</v>
           </cell>
           <cell r="D74">
-            <v>46386</v>
+            <v>46371</v>
           </cell>
         </row>
         <row r="75">
           <cell r="B75" t="str">
-            <v>UPS Installation</v>
-          </cell>
-          <cell r="C75" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D75">
-            <v>46386</v>
+            <v>PTTS</v>
           </cell>
         </row>
         <row r="76">
           <cell r="B76" t="str">
-            <v>DB Dresssing</v>
+            <v>Pipe accessories fixing &amp; testing</v>
           </cell>
           <cell r="C76" t="str">
             <v>WIP</v>
@@ -1769,512 +1376,7 @@
             <v>46386</v>
           </cell>
         </row>
-        <row r="77">
-          <cell r="B77" t="str">
-            <v>PHE</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78" t="str">
-            <v>Cister&amp; Sensor Fixing</v>
-          </cell>
-          <cell r="C78" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D78">
-            <v>46305</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79" t="str">
-            <v>HVAC</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80" t="str">
-            <v>Duct testinfg &amp; dropper for diffusere</v>
-          </cell>
-          <cell r="C80" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D80">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81" t="str">
-            <v>Pipe Testing</v>
-          </cell>
-          <cell r="C81" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D81">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82" t="str">
-            <v>AHU Connection</v>
-          </cell>
-          <cell r="C82" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D82">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83" t="str">
-            <v>Firefighting</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84" t="str">
-            <v>Sprinkler Flexible connection &amp; testing</v>
-          </cell>
-          <cell r="C84" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D84">
-            <v>46305</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85" t="str">
-            <v>Wet Riser &amp; FHC installation</v>
-          </cell>
-          <cell r="C85" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D85">
-            <v>46305</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="B86" t="str">
-            <v>ELV</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87" t="str">
-            <v>CAT 6 cabling</v>
-          </cell>
-          <cell r="C87" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D87">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="B88" t="str">
-            <v>PA &amp; FAS cabling</v>
-          </cell>
-          <cell r="C88" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D88">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89" t="str">
-            <v>Fire Panel Installation</v>
-          </cell>
-          <cell r="C89" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D89">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="B90" t="str">
-            <v>Network Switch Installation &amp; connection</v>
-          </cell>
-          <cell r="C90" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D90">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="B91" t="str">
-            <v>MGPS</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="B92" t="str">
-            <v>Copper Pipe testing</v>
-          </cell>
-          <cell r="C92" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D92">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="B93" t="str">
-            <v>PTTS</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="B94" t="str">
-            <v>Pipe accessories fixing &amp; testing</v>
-          </cell>
-          <cell r="C94" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D94">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="B95" t="str">
-            <v>Final Fixture</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="B96" t="str">
-            <v>Electrical</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="B97" t="str">
-            <v>Switch Socket &amp; light fixture  Installation</v>
-          </cell>
-          <cell r="C97" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D97">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="B98" t="str">
-            <v>Cable termination &amp; panel testing</v>
-          </cell>
-          <cell r="C98" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D98">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="B99" t="str">
-            <v>UPS testing &amp; commissioning</v>
-          </cell>
-          <cell r="C99" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D99">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="B100" t="str">
-            <v>DB testing</v>
-          </cell>
-          <cell r="C100" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D100">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="B101" t="str">
-            <v>PHE</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="B102" t="str">
-            <v>Fixtures Installation</v>
-          </cell>
-          <cell r="C102" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D102">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="B103" t="str">
-            <v>HVAC</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="B104" t="str">
-            <v>Diffuser Installation</v>
-          </cell>
-          <cell r="C104" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D104">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="B105" t="str">
-            <v>AHU Testing</v>
-          </cell>
-          <cell r="C105" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D105">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="B106" t="str">
-            <v>Firefighting</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="B107" t="str">
-            <v>Sprinkler Fixing</v>
-          </cell>
-          <cell r="C107" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D107">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="B108" t="str">
-            <v>ELV</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="B109" t="str">
-            <v xml:space="preserve"> Fire Alam  &amp; PA Device Fixing</v>
-          </cell>
-          <cell r="C109" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D109">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="B110" t="str">
-            <v xml:space="preserve"> Telephone &amp; Data Socket Fixing</v>
-          </cell>
-          <cell r="C110" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D110">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="B111" t="str">
-            <v>Fire Panel testing &amp; device addressing</v>
-          </cell>
-          <cell r="C111" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D111">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="B112" t="str">
-            <v>Network Switch testing</v>
-          </cell>
-          <cell r="C112" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D112">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="B113" t="str">
-            <v>QMS , HMIS , Biometric , etc.</v>
-          </cell>
-          <cell r="C113" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D113">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="B114" t="str">
-            <v>MGPS</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="B115" t="str">
-            <v>Outlet Installation</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="B116" t="str">
-            <v>PTTS</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="B117" t="str">
-            <v>PTTS station installation</v>
-          </cell>
-          <cell r="C117" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D117">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="B118" t="str">
-            <v>Terrace</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="B119" t="str">
-            <v xml:space="preserve"> PHE Piping installation</v>
-          </cell>
-          <cell r="C119" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D119">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="B120" t="str">
-            <v>AHU Installation</v>
-          </cell>
-          <cell r="C120" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D120">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="B121" t="str">
-            <v>Fan Installation</v>
-          </cell>
-          <cell r="C121" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D121">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="B122" t="str">
-            <v>Cable Tray, Raceway Installation &amp; cable laying</v>
-          </cell>
-          <cell r="C122" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D122">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="B123" t="str">
-            <v>Solar Panel Installation</v>
-          </cell>
-          <cell r="C123" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D123">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="B124" t="str">
-            <v>DDC Panel Installation</v>
-          </cell>
-          <cell r="C124" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D124">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="B125" t="str">
-            <v>Booster Panel Installation</v>
-          </cell>
-          <cell r="C125" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D125">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="B126" t="str">
-            <v>Shaft</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="B127" t="str">
-            <v>PHE Piping</v>
-          </cell>
-          <cell r="C127" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D127">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="B128" t="str">
-            <v>HVAC Ducting</v>
-          </cell>
-          <cell r="C128" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D128">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="B129" t="str">
-            <v>Rising Main Installation</v>
-          </cell>
-          <cell r="C129" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D129">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="B130" t="str">
-            <v>Cable Tray &amp; Raceway installation</v>
-          </cell>
-          <cell r="C130" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D130">
-            <v>46386</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="B131" t="str">
-            <v>Lift Installation</v>
-          </cell>
-          <cell r="C131" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D131">
-            <v>46386</v>
-          </cell>
-        </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2288,221 +1390,614 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="EMR"/>
-      <sheetName val="Sheet1"/>
       <sheetName val="OPD"/>
+      <sheetName val="IPD"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>OPD Balance Activities Schedule (11-Sep-2026)</v>
+      <sheetData sheetId="0">
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>Brickwork</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D7">
+            <v>46320</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>Plaster</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D8">
+            <v>46336</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>Ground Floor</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D9">
+            <v>46325</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>1st Floor</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D10">
+            <v>46315</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>2nd Floor</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D11">
+            <v>46310</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>3rd Floor</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D12">
+            <v>46310</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>Above terrace</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D13">
+            <v>46336</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>Aluminum Joineries</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D14">
+            <v>46371</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>Fire door frame &amp; shutter</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D15">
+            <v>46371</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Flooring &amp; dado</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D16">
+            <v>46356</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>False Ceiling</v>
+          </cell>
+          <cell r="C17">
+            <v>46310</v>
+          </cell>
+          <cell r="D17">
+            <v>46370</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>Ground Floor</v>
+          </cell>
+          <cell r="C18">
+            <v>46310</v>
+          </cell>
+          <cell r="D18">
+            <v>46325</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>1st Floor</v>
+          </cell>
+          <cell r="C19">
+            <v>46325</v>
+          </cell>
+          <cell r="D19">
+            <v>46340</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>2nd Floor</v>
+          </cell>
+          <cell r="C20">
+            <v>46340</v>
+          </cell>
+          <cell r="D20">
+            <v>46355</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>3rd Floor</v>
+          </cell>
+          <cell r="C21">
+            <v>46355</v>
+          </cell>
+          <cell r="D21">
+            <v>46370</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Lift facia granite</v>
+          </cell>
+          <cell r="C22">
+            <v>46315</v>
+          </cell>
+          <cell r="D22">
+            <v>46350</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v xml:space="preserve">Courtyard Plaster </v>
+          </cell>
+          <cell r="C23">
+            <v>46293</v>
+          </cell>
+          <cell r="D23">
+            <v>46325</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>SS Handrail</v>
+          </cell>
+          <cell r="C24">
+            <v>46336</v>
+          </cell>
+          <cell r="D24">
+            <v>46372</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>Over Terrace</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>OHT&amp;Mummty</v>
+          </cell>
+          <cell r="C26">
+            <v>46290</v>
+          </cell>
+          <cell r="D26">
+            <v>46310</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>OHT Waterproofing &amp; Tiling</v>
+          </cell>
+          <cell r="C27">
+            <v>46315</v>
+          </cell>
+          <cell r="D27">
+            <v>46327</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>LMR</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D28">
+            <v>46311</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>Terrace Waterproofing&amp;HRT Tiles</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D29">
+            <v>46320</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>Pedestals</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D30">
+            <v>46325</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>Polycarbonate Sheet</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D31">
+            <v>46320</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>External</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Shaft brickwork &amp; plaster</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Elevation A</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D34">
+            <v>46320</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>Elevation B</v>
+          </cell>
+          <cell r="C35">
+            <v>46295</v>
+          </cell>
+          <cell r="D35">
+            <v>46326</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>Elevation C</v>
+          </cell>
+          <cell r="C36">
+            <v>46283</v>
+          </cell>
+          <cell r="D36">
+            <v>46295</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>Elevation D</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D37">
+            <v>46305</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>External Stone Cladding</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>Elevation A</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>Elevation B</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>Elevation C</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>Elevation D</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>Structural Glazing</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>Elevation A</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>Elevation B</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>Elevation C</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>Elevation D</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>MEP</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49" t="str">
+            <v>Frist Fix</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50" t="str">
+            <v>Electrical</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51" t="str">
+            <v>Wall Conduit &amp; GI Box Fixing</v>
+          </cell>
+          <cell r="C51" t="str">
+            <v xml:space="preserve">Completed </v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52" t="str">
+            <v>Cable Tray Installation</v>
+          </cell>
+          <cell r="C52" t="str">
+            <v xml:space="preserve">Completed </v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53" t="str">
+            <v>DB Installation</v>
+          </cell>
+          <cell r="C53" t="str">
+            <v xml:space="preserve">Completed </v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
-            <v>Electrical</v>
+            <v>PHE</v>
           </cell>
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>Wiring</v>
+            <v>CI Pipiing</v>
           </cell>
           <cell r="C55" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D55">
-            <v>46325</v>
+            <v>46366</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Cable Laying &amp; Panel Installation</v>
+            <v>CPVC Piping</v>
           </cell>
           <cell r="C56" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D56">
-            <v>46325</v>
+            <v>46366</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
-            <v>UPS Installation</v>
-          </cell>
-          <cell r="C57">
-            <v>46291</v>
+            <v>GI Piping</v>
+          </cell>
+          <cell r="C57" t="str">
+            <v>WIP</v>
           </cell>
           <cell r="D57">
-            <v>46305</v>
+            <v>46366</v>
           </cell>
         </row>
         <row r="58">
           <cell r="B58" t="str">
-            <v>DB Dresssing</v>
-          </cell>
-          <cell r="C58" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D58">
-            <v>46336</v>
+            <v>HVAC</v>
           </cell>
         </row>
         <row r="59">
           <cell r="B59" t="str">
-            <v>PHE</v>
+            <v>Ducting &amp; Insulation</v>
+          </cell>
+          <cell r="C59" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D59">
+            <v>46326</v>
           </cell>
         </row>
         <row r="60">
           <cell r="B60" t="str">
-            <v>Cister&amp; Sensor Fixing</v>
+            <v>Piping installation</v>
           </cell>
           <cell r="C60" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D60">
-            <v>46288</v>
+            <v>46326</v>
           </cell>
         </row>
         <row r="61">
           <cell r="B61" t="str">
-            <v>HVAC</v>
+            <v>AHU Installation</v>
+          </cell>
+          <cell r="C61" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D61">
+            <v>46326</v>
           </cell>
         </row>
         <row r="62">
           <cell r="B62" t="str">
-            <v>Duct testinfg &amp; dropper for diffusere</v>
-          </cell>
-          <cell r="C62" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D62">
-            <v>46366</v>
+            <v>Firefighting</v>
           </cell>
         </row>
         <row r="63">
           <cell r="B63" t="str">
-            <v>Pipe Testing</v>
+            <v>Piping installation</v>
           </cell>
           <cell r="C63" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D63">
-            <v>46310</v>
+            <v>46358</v>
           </cell>
         </row>
         <row r="64">
           <cell r="B64" t="str">
-            <v>AHU Connection</v>
-          </cell>
-          <cell r="C64" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D64">
-            <v>46311</v>
+            <v>ELV</v>
           </cell>
         </row>
         <row r="65">
           <cell r="B65" t="str">
-            <v>Firefighting</v>
+            <v>PVC conduiting &amp; GI box fixing</v>
+          </cell>
+          <cell r="C65" t="str">
+            <v xml:space="preserve">Completed </v>
           </cell>
         </row>
         <row r="66">
           <cell r="B66" t="str">
-            <v>Sprinkler Flexible connection &amp; testing</v>
+            <v>Raceway Installation</v>
           </cell>
           <cell r="C66" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D66">
-            <v>46340</v>
+            <v xml:space="preserve">Completed </v>
           </cell>
         </row>
         <row r="67">
           <cell r="B67" t="str">
-            <v>Wet Riser &amp; FHC installation</v>
-          </cell>
-          <cell r="C67" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D67">
-            <v>46319</v>
+            <v>MGPS</v>
           </cell>
         </row>
         <row r="68">
           <cell r="B68" t="str">
-            <v>ELV</v>
+            <v>Copper Pipning</v>
           </cell>
         </row>
         <row r="69">
           <cell r="B69" t="str">
-            <v>CAT 6 cabling</v>
+            <v>PTTS</v>
           </cell>
           <cell r="C69" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D69">
-            <v>46341</v>
+            <v>46366</v>
           </cell>
         </row>
         <row r="70">
           <cell r="B70" t="str">
-            <v>PA &amp; FAS cabling</v>
+            <v>Pipe Installation</v>
           </cell>
           <cell r="C70" t="str">
             <v>WIP</v>
           </cell>
           <cell r="D70">
-            <v>46341</v>
+            <v>46366</v>
           </cell>
         </row>
         <row r="71">
           <cell r="B71" t="str">
-            <v>Fire Panel Installation</v>
-          </cell>
-          <cell r="C71">
-            <v>46291</v>
-          </cell>
-          <cell r="D71">
-            <v>46295</v>
+            <v>Second Fix</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72" t="str">
-            <v>Network Switch Installation &amp; connection</v>
-          </cell>
-          <cell r="C72" t="str">
-            <v>WIP</v>
-          </cell>
-          <cell r="D72">
-            <v>46346</v>
+            <v>Electrical</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73" t="str">
-            <v>MGPS</v>
+            <v>Wiring</v>
+          </cell>
+          <cell r="C73" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D73">
+            <v>46386</v>
           </cell>
         </row>
         <row r="74">
           <cell r="B74" t="str">
-            <v>Copper Pipe testing</v>
-          </cell>
-          <cell r="C74">
-            <v>46310</v>
+            <v>Cable Laying &amp; Panel Installation</v>
+          </cell>
+          <cell r="C74" t="str">
+            <v>WIP</v>
           </cell>
           <cell r="D74">
-            <v>46371</v>
+            <v>46386</v>
           </cell>
         </row>
         <row r="75">
           <cell r="B75" t="str">
-            <v>PTTS</v>
+            <v>UPS Installation</v>
+          </cell>
+          <cell r="C75" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D75">
+            <v>46386</v>
           </cell>
         </row>
         <row r="76">
           <cell r="B76" t="str">
-            <v>Pipe accessories fixing &amp; testing</v>
+            <v>DB Dresssing</v>
           </cell>
           <cell r="C76" t="str">
             <v>WIP</v>
@@ -2511,7 +2006,512 @@
             <v>46386</v>
           </cell>
         </row>
+        <row r="77">
+          <cell r="B77" t="str">
+            <v>PHE</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="B78" t="str">
+            <v>Cister&amp; Sensor Fixing</v>
+          </cell>
+          <cell r="C78" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D78">
+            <v>46305</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="B79" t="str">
+            <v>HVAC</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="B80" t="str">
+            <v>Duct testinfg &amp; dropper for diffusere</v>
+          </cell>
+          <cell r="C80" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D80">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="B81" t="str">
+            <v>Pipe Testing</v>
+          </cell>
+          <cell r="C81" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D81">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="B82" t="str">
+            <v>AHU Connection</v>
+          </cell>
+          <cell r="C82" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D82">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="B83" t="str">
+            <v>Firefighting</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="B84" t="str">
+            <v>Sprinkler Flexible connection &amp; testing</v>
+          </cell>
+          <cell r="C84" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D84">
+            <v>46305</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="B85" t="str">
+            <v>Wet Riser &amp; FHC installation</v>
+          </cell>
+          <cell r="C85" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D85">
+            <v>46305</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="B86" t="str">
+            <v>ELV</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="B87" t="str">
+            <v>CAT 6 cabling</v>
+          </cell>
+          <cell r="C87" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D87">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="B88" t="str">
+            <v>PA &amp; FAS cabling</v>
+          </cell>
+          <cell r="C88" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D88">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="B89" t="str">
+            <v>Fire Panel Installation</v>
+          </cell>
+          <cell r="C89" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D89">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="B90" t="str">
+            <v>Network Switch Installation &amp; connection</v>
+          </cell>
+          <cell r="C90" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D90">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="B91" t="str">
+            <v>MGPS</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="B92" t="str">
+            <v>Copper Pipe testing</v>
+          </cell>
+          <cell r="C92" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D92">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="B93" t="str">
+            <v>PTTS</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="B94" t="str">
+            <v>Pipe accessories fixing &amp; testing</v>
+          </cell>
+          <cell r="C94" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D94">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="B95" t="str">
+            <v>Final Fixture</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="B96" t="str">
+            <v>Electrical</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="B97" t="str">
+            <v>Switch Socket &amp; light fixture  Installation</v>
+          </cell>
+          <cell r="C97" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D97">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="B98" t="str">
+            <v>Cable termination &amp; panel testing</v>
+          </cell>
+          <cell r="C98" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D98">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="B99" t="str">
+            <v>UPS testing &amp; commissioning</v>
+          </cell>
+          <cell r="C99" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D99">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="B100" t="str">
+            <v>DB testing</v>
+          </cell>
+          <cell r="C100" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D100">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="B101" t="str">
+            <v>PHE</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="B102" t="str">
+            <v>Fixtures Installation</v>
+          </cell>
+          <cell r="C102" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D102">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="B103" t="str">
+            <v>HVAC</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="B104" t="str">
+            <v>Diffuser Installation</v>
+          </cell>
+          <cell r="C104" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D104">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="B105" t="str">
+            <v>AHU Testing</v>
+          </cell>
+          <cell r="C105" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D105">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="B106" t="str">
+            <v>Firefighting</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="B107" t="str">
+            <v>Sprinkler Fixing</v>
+          </cell>
+          <cell r="C107" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D107">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="B108" t="str">
+            <v>ELV</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="B109" t="str">
+            <v xml:space="preserve"> Fire Alam  &amp; PA Device Fixing</v>
+          </cell>
+          <cell r="C109" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D109">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="B110" t="str">
+            <v xml:space="preserve"> Telephone &amp; Data Socket Fixing</v>
+          </cell>
+          <cell r="C110" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D110">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="B111" t="str">
+            <v>Fire Panel testing &amp; device addressing</v>
+          </cell>
+          <cell r="C111" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D111">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="B112" t="str">
+            <v>Network Switch testing</v>
+          </cell>
+          <cell r="C112" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D112">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="B113" t="str">
+            <v>QMS , HMIS , Biometric , etc.</v>
+          </cell>
+          <cell r="C113" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D113">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="B114" t="str">
+            <v>MGPS</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="B115" t="str">
+            <v>Outlet Installation</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="B116" t="str">
+            <v>PTTS</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="B117" t="str">
+            <v>PTTS station installation</v>
+          </cell>
+          <cell r="C117" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D117">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="B118" t="str">
+            <v>Terrace</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="B119" t="str">
+            <v xml:space="preserve"> PHE Piping installation</v>
+          </cell>
+          <cell r="C119" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D119">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="B120" t="str">
+            <v>AHU Installation</v>
+          </cell>
+          <cell r="C120" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D120">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="B121" t="str">
+            <v>Fan Installation</v>
+          </cell>
+          <cell r="C121" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D121">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="B122" t="str">
+            <v>Cable Tray, Raceway Installation &amp; cable laying</v>
+          </cell>
+          <cell r="C122" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D122">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="B123" t="str">
+            <v>Solar Panel Installation</v>
+          </cell>
+          <cell r="C123" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D123">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="B124" t="str">
+            <v>DDC Panel Installation</v>
+          </cell>
+          <cell r="C124" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D124">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="B125" t="str">
+            <v>Booster Panel Installation</v>
+          </cell>
+          <cell r="C125" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D125">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="B126" t="str">
+            <v>Shaft</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="B127" t="str">
+            <v>PHE Piping</v>
+          </cell>
+          <cell r="C127" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D127">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="B128" t="str">
+            <v>HVAC Ducting</v>
+          </cell>
+          <cell r="C128" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D128">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="B129" t="str">
+            <v>Rising Main Installation</v>
+          </cell>
+          <cell r="C129" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D129">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="B130" t="str">
+            <v>Cable Tray &amp; Raceway installation</v>
+          </cell>
+          <cell r="C130" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D130">
+            <v>46386</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="B131" t="str">
+            <v>Lift Installation</v>
+          </cell>
+          <cell r="C131" t="str">
+            <v>WIP</v>
+          </cell>
+          <cell r="D131">
+            <v>46386</v>
+          </cell>
+        </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2778,25 +2778,25 @@
       <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:12" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="69" t="s">
+      <c r="A2" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="70" t="s">
         <v>102</v>
       </c>
       <c r="H2" s="61" t="s">
@@ -2816,18 +2816,18 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="62"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="65"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="69"/>
       <c r="F3" s="71"/>
       <c r="G3" s="71"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -4907,7 +4907,7 @@
         <v>46244</v>
       </c>
       <c r="C61" s="28">
-        <f>VLOOKUP(A61,[2]OPD!$B$54:$D$76,3,FALSE)</f>
+        <f>VLOOKUP(A61,[1]OPD!$B$54:$D$76,3,FALSE)</f>
         <v>46341</v>
       </c>
       <c r="D61" s="39" t="s">
@@ -5318,20 +5318,20 @@
       <c r="L71" s="37"/>
     </row>
     <row r="72" spans="1:12" s="1" customFormat="1" ht="22.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="68" t="s">
+      <c r="A72" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="B72" s="68"/>
-      <c r="C72" s="68"/>
-      <c r="D72" s="68"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="68"/>
-      <c r="H72" s="68"/>
-      <c r="I72" s="68"/>
-      <c r="J72" s="68"/>
-      <c r="K72" s="68"/>
-      <c r="L72" s="68"/>
+      <c r="B72" s="63"/>
+      <c r="C72" s="63"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63"/>
+      <c r="J72" s="63"/>
+      <c r="K72" s="63"/>
+      <c r="L72" s="63"/>
     </row>
     <row r="73" spans="1:12" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A73" s="13" t="s">
@@ -5763,28 +5763,28 @@
       <c r="Q2" s="6"/>
     </row>
     <row r="3" spans="1:17" s="5" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="63" t="s">
+      <c r="A3" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="67" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="G3" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="66" t="s">
+      <c r="H3" s="70" t="s">
         <v>29</v>
       </c>
       <c r="I3" s="61" t="s">
@@ -5798,14 +5798,14 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="38.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
       <c r="E4" s="61"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
       <c r="I4" s="61"/>
       <c r="J4" s="61"/>
       <c r="K4" s="61"/>
@@ -5951,7 +5951,7 @@
         <v>46073</v>
       </c>
       <c r="C9" s="39">
-        <f>VLOOKUP(A9,[1]EMR!$B$7:$D$131,3,FALSE)</f>
+        <f>VLOOKUP(A9,[2]EMR!$B$7:$D$131,3,FALSE)</f>
         <v>46356</v>
       </c>
       <c r="D9" s="39" t="s">
